--- a/00 Reference Document/config/ISL metadata.xlsx
+++ b/00 Reference Document/config/ISL metadata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Metadata_CBM07WI5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Smart Maintanence\TOV1050_Analyzer\00 Reference Document\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDC1FED4-38C6-41DA-9C4A-2AABC43E0AE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94D3D5B9-60DB-40DA-B91B-30C237A8E39D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{40971268-6843-45A4-929F-390CE8EC23ED}"/>
+    <workbookView xWindow="0" yWindow="100" windowWidth="21600" windowHeight="11180" activeTab="2" xr2:uid="{40971268-6843-45A4-929F-390CE8EC23ED}"/>
   </bookViews>
   <sheets>
     <sheet name="threshold" sheetId="3" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="location type" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'DT track type'!$A$548:$D$548</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'DT track type'!$A$545:$D$545</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">threshold!$A$1:$F$89</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'UT track type'!$A$1:$D$1</definedName>
   </definedNames>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1613" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1610" uniqueCount="40">
   <si>
     <t>Location Type</t>
   </si>
@@ -244,7 +244,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -266,9 +266,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -276,7 +273,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -307,9 +303,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -347,7 +343,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -453,7 +449,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -595,7 +591,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -607,12 +603,12 @@
   <dimension ref="A1:F89"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15" style="13" customWidth="1"/>
-    <col min="2" max="2" width="14.453125" style="13" customWidth="1"/>
-    <col min="3" max="3" width="15.81640625" style="13" customWidth="1"/>
-    <col min="4" max="4" width="9.1796875" style="13"/>
-    <col min="5" max="5" width="9.1796875" style="13" customWidth="1"/>
-    <col min="6" max="6" width="39.81640625" style="13" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="14.453125" customWidth="1"/>
+    <col min="3" max="3" width="15.81640625" customWidth="1"/>
+    <col min="4" max="4" width="9.1796875"/>
+    <col min="5" max="5" width="9.1796875" customWidth="1"/>
+    <col min="6" max="6" width="39.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
@@ -636,775 +632,775 @@
       </c>
     </row>
     <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" s="11" t="s">
+      <c r="B2" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="11">
+      <c r="D2" s="10">
         <v>350</v>
       </c>
-      <c r="E2" s="11"/>
-      <c r="F2" s="12" t="s">
+      <c r="E2" s="10"/>
+      <c r="F2" s="11" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" s="11" t="s">
+      <c r="B3" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="11">
+      <c r="D3" s="10">
         <v>280</v>
       </c>
-      <c r="E3" s="11">
+      <c r="E3" s="10">
         <v>350</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="11" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="11" t="s">
+      <c r="B4" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="10">
         <v>250</v>
       </c>
-      <c r="E4" s="11">
+      <c r="E4" s="10">
         <v>280</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="11" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="11" t="s">
+      <c r="B5" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11">
+      <c r="D5" s="10"/>
+      <c r="E5" s="10">
         <v>250</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="11" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="11" t="s">
+      <c r="B6" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="10">
         <v>350</v>
       </c>
-      <c r="E6" s="11"/>
-      <c r="F6" s="12" t="s">
+      <c r="E6" s="10"/>
+      <c r="F6" s="11" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="11" t="s">
+      <c r="B7" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="10">
         <v>280</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="10">
         <v>350</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="11" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="11" t="s">
+      <c r="B8" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="10">
         <v>250</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="10">
         <v>280</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="11" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="11" t="s">
+      <c r="B9" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11">
+      <c r="D9" s="10"/>
+      <c r="E9" s="10">
         <v>250</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="11" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="11" t="s">
+      <c r="B10" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11">
+      <c r="D10" s="10"/>
+      <c r="E10" s="10">
         <v>7.24</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="11" t="s">
+      <c r="B11" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="10">
         <v>0</v>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="10">
         <v>0</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" s="11" t="s">
+      <c r="B12" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11">
+      <c r="D12" s="10"/>
+      <c r="E12" s="10">
         <v>7.24</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F12" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" s="11" t="s">
+      <c r="B13" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="10">
         <v>0</v>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="10">
         <v>0</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F13" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" s="11" t="s">
+      <c r="B14" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="10">
         <v>3880</v>
       </c>
-      <c r="E14" s="11">
+      <c r="E14" s="10">
         <v>3900</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="F14" s="11" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C15" s="11" t="s">
+      <c r="B15" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11">
+      <c r="D15" s="10"/>
+      <c r="E15" s="10">
         <v>3880</v>
       </c>
-      <c r="F15" s="12" t="s">
+      <c r="F15" s="11" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C16" s="11" t="s">
+      <c r="B16" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="11">
+      <c r="D16" s="10">
         <v>3880</v>
       </c>
-      <c r="E16" s="11">
+      <c r="E16" s="10">
         <v>3900</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="F16" s="11" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17" s="11" t="s">
+      <c r="B17" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11">
+      <c r="D17" s="10"/>
+      <c r="E17" s="10">
         <v>3880</v>
       </c>
-      <c r="F17" s="12" t="s">
+      <c r="F17" s="11" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="C18" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="12">
         <v>3880</v>
       </c>
-      <c r="E18" s="14">
+      <c r="E18" s="12">
         <v>3900</v>
       </c>
-      <c r="F18" s="16" t="s">
+      <c r="F18" s="14" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="14" t="s">
+      <c r="C19" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14">
+      <c r="D19" s="12"/>
+      <c r="E19" s="12">
         <v>3880</v>
       </c>
-      <c r="F19" s="16" t="s">
+      <c r="F19" s="14" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="14" t="s">
+      <c r="A20" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="C20" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="12">
         <v>3880</v>
       </c>
-      <c r="E20" s="14">
+      <c r="E20" s="12">
         <v>3900</v>
       </c>
-      <c r="F20" s="16" t="s">
+      <c r="F20" s="14" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C21" s="14" t="s">
+      <c r="C21" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14">
+      <c r="D21" s="12"/>
+      <c r="E21" s="12">
         <v>3880</v>
       </c>
-      <c r="F21" s="16" t="s">
+      <c r="F21" s="14" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="14" t="s">
+      <c r="C22" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="12">
         <v>3880</v>
       </c>
-      <c r="E22" s="14">
+      <c r="E22" s="12">
         <v>3900</v>
       </c>
-      <c r="F22" s="16" t="s">
+      <c r="F22" s="14" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="14" t="s">
+      <c r="A23" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C23" s="14" t="s">
+      <c r="C23" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14">
+      <c r="D23" s="12"/>
+      <c r="E23" s="12">
         <v>3880</v>
       </c>
-      <c r="F23" s="16" t="s">
+      <c r="F23" s="14" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="14" t="s">
+      <c r="A24" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C24" s="14" t="s">
+      <c r="C24" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="14">
+      <c r="D24" s="12">
         <v>3880</v>
       </c>
-      <c r="E24" s="14">
+      <c r="E24" s="12">
         <v>3900</v>
       </c>
-      <c r="F24" s="16" t="s">
+      <c r="F24" s="14" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="14" t="s">
+      <c r="A25" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C25" s="14" t="s">
+      <c r="C25" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14">
+      <c r="D25" s="12"/>
+      <c r="E25" s="12">
         <v>3880</v>
       </c>
-      <c r="F25" s="16" t="s">
+      <c r="F25" s="14" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="14" t="s">
+      <c r="A26" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="14" t="s">
+      <c r="C26" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="D26" s="14">
+      <c r="D26" s="12">
         <v>300</v>
       </c>
-      <c r="E26" s="14"/>
-      <c r="F26" s="18" t="s">
+      <c r="E26" s="12"/>
+      <c r="F26" s="16" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="14" t="s">
+      <c r="A27" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C27" s="14" t="s">
+      <c r="C27" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D27" s="14">
+      <c r="D27" s="12">
         <v>230</v>
       </c>
-      <c r="E27" s="14">
+      <c r="E27" s="12">
         <v>300</v>
       </c>
-      <c r="F27" s="18" t="s">
+      <c r="F27" s="16" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="14" t="s">
+      <c r="A28" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="15" t="s">
+      <c r="B28" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C28" s="14" t="s">
+      <c r="C28" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D28" s="14">
+      <c r="D28" s="12">
         <v>200</v>
       </c>
-      <c r="E28" s="14">
+      <c r="E28" s="12">
         <v>230</v>
       </c>
-      <c r="F28" s="18" t="s">
+      <c r="F28" s="16" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A29" s="14" t="s">
+      <c r="A29" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="15" t="s">
+      <c r="B29" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C29" s="14" t="s">
+      <c r="C29" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14">
+      <c r="D29" s="12"/>
+      <c r="E29" s="12">
         <v>200</v>
       </c>
-      <c r="F29" s="18" t="s">
+      <c r="F29" s="16" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="14" t="s">
+      <c r="A30" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="14" t="s">
+      <c r="C30" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="D30" s="14">
+      <c r="D30" s="12">
         <v>300</v>
       </c>
-      <c r="E30" s="14"/>
-      <c r="F30" s="18" t="s">
+      <c r="E30" s="12"/>
+      <c r="F30" s="16" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="14" t="s">
+      <c r="A31" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C31" s="14" t="s">
+      <c r="C31" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D31" s="14">
+      <c r="D31" s="12">
         <v>230</v>
       </c>
-      <c r="E31" s="14">
+      <c r="E31" s="12">
         <v>300</v>
       </c>
-      <c r="F31" s="18" t="s">
+      <c r="F31" s="16" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="14" t="s">
+      <c r="A32" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="15" t="s">
+      <c r="B32" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C32" s="14" t="s">
+      <c r="C32" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D32" s="14">
+      <c r="D32" s="12">
         <v>200</v>
       </c>
-      <c r="E32" s="14">
+      <c r="E32" s="12">
         <v>230</v>
       </c>
-      <c r="F32" s="18" t="s">
+      <c r="F32" s="16" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A33" s="14" t="s">
+      <c r="A33" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="15" t="s">
+      <c r="B33" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C33" s="14" t="s">
+      <c r="C33" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14">
+      <c r="D33" s="12"/>
+      <c r="E33" s="12">
         <v>200</v>
       </c>
-      <c r="F33" s="18" t="s">
+      <c r="F33" s="16" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="14" t="s">
+      <c r="A34" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="14" t="s">
+      <c r="C34" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="D34" s="14">
+      <c r="D34" s="12">
         <v>200</v>
       </c>
-      <c r="E34" s="14"/>
-      <c r="F34" s="18" t="s">
+      <c r="E34" s="12"/>
+      <c r="F34" s="16" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="14" t="s">
+      <c r="A35" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="15" t="s">
+      <c r="B35" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C35" s="14" t="s">
+      <c r="C35" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D35" s="14">
+      <c r="D35" s="12">
         <v>130</v>
       </c>
-      <c r="E35" s="14">
+      <c r="E35" s="12">
         <v>200</v>
       </c>
-      <c r="F35" s="18" t="s">
+      <c r="F35" s="16" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="14" t="s">
+      <c r="A36" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="15" t="s">
+      <c r="B36" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C36" s="14" t="s">
+      <c r="C36" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D36" s="14">
+      <c r="D36" s="12">
         <v>100</v>
       </c>
-      <c r="E36" s="14">
+      <c r="E36" s="12">
         <v>130</v>
       </c>
-      <c r="F36" s="18" t="s">
+      <c r="F36" s="16" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A37" s="14" t="s">
+      <c r="A37" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B37" s="15" t="s">
+      <c r="B37" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C37" s="14" t="s">
+      <c r="C37" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14">
+      <c r="D37" s="12"/>
+      <c r="E37" s="12">
         <v>100</v>
       </c>
-      <c r="F37" s="18" t="s">
+      <c r="F37" s="16" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="38" spans="1:6" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="14" t="s">
+    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="15" t="s">
+      <c r="B38" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C38" s="14" t="s">
+      <c r="C38" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="D38" s="14">
+      <c r="D38" s="12">
         <v>260</v>
       </c>
-      <c r="E38" s="14"/>
-      <c r="F38" s="18" t="s">
+      <c r="E38" s="12"/>
+      <c r="F38" s="16" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:6" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="14" t="s">
+    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="15" t="s">
+      <c r="B39" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C39" s="14" t="s">
+      <c r="C39" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D39" s="14">
+      <c r="D39" s="12">
         <v>190</v>
       </c>
-      <c r="E39" s="14">
+      <c r="E39" s="12">
         <v>260</v>
       </c>
-      <c r="F39" s="18" t="s">
+      <c r="F39" s="16" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="40" spans="1:6" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="14" t="s">
+    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="15" t="s">
+      <c r="B40" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C40" s="14" t="s">
+      <c r="C40" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D40" s="14">
+      <c r="D40" s="12">
         <v>160</v>
       </c>
-      <c r="E40" s="14">
+      <c r="E40" s="12">
         <v>190</v>
       </c>
-      <c r="F40" s="18" t="s">
+      <c r="F40" s="16" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="41" spans="1:6" s="13" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="14" t="s">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A41" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B41" s="15" t="s">
+      <c r="B41" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C41" s="14" t="s">
+      <c r="C41" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E41" s="14">
+      <c r="E41" s="12">
         <v>160</v>
       </c>
-      <c r="F41" s="18" t="s">
+      <c r="F41" s="16" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="13" t="s">
+      <c r="A42" t="s">
         <v>12</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C42" s="13" t="s">
+      <c r="C42" t="s">
         <v>8</v>
       </c>
-      <c r="D42" s="13">
+      <c r="D42">
         <v>300</v>
       </c>
       <c r="F42" s="4" t="s">
@@ -1412,19 +1408,19 @@
       </c>
     </row>
     <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="13" t="s">
+      <c r="A43" t="s">
         <v>12</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C43" s="13" t="s">
+      <c r="C43" t="s">
         <v>9</v>
       </c>
-      <c r="D43" s="13">
+      <c r="D43">
         <v>230</v>
       </c>
-      <c r="E43" s="13">
+      <c r="E43">
         <v>300</v>
       </c>
       <c r="F43" s="4" t="s">
@@ -1432,19 +1428,19 @@
       </c>
     </row>
     <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="13" t="s">
+      <c r="A44" t="s">
         <v>12</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C44" s="13" t="s">
+      <c r="C44" t="s">
         <v>10</v>
       </c>
-      <c r="D44" s="13">
+      <c r="D44">
         <v>200</v>
       </c>
-      <c r="E44" s="13">
+      <c r="E44">
         <v>230</v>
       </c>
       <c r="F44" s="4" t="s">
@@ -1452,16 +1448,16 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A45" s="13" t="s">
+      <c r="A45" t="s">
         <v>12</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C45" s="13" t="s">
+      <c r="C45" t="s">
         <v>11</v>
       </c>
-      <c r="E45" s="13">
+      <c r="E45">
         <v>200</v>
       </c>
       <c r="F45" s="4" t="s">
@@ -1469,16 +1465,16 @@
       </c>
     </row>
     <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="13" t="s">
+      <c r="A46" t="s">
         <v>12</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C46" s="13" t="s">
+      <c r="C46" t="s">
         <v>8</v>
       </c>
-      <c r="D46" s="13">
+      <c r="D46">
         <v>300</v>
       </c>
       <c r="F46" s="4" t="s">
@@ -1486,19 +1482,19 @@
       </c>
     </row>
     <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="13" t="s">
+      <c r="A47" t="s">
         <v>12</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C47" s="13" t="s">
+      <c r="C47" t="s">
         <v>9</v>
       </c>
-      <c r="D47" s="13">
+      <c r="D47">
         <v>230</v>
       </c>
-      <c r="E47" s="13">
+      <c r="E47">
         <v>300</v>
       </c>
       <c r="F47" s="4" t="s">
@@ -1506,19 +1502,19 @@
       </c>
     </row>
     <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="13" t="s">
+      <c r="A48" t="s">
         <v>12</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C48" s="13" t="s">
+      <c r="C48" t="s">
         <v>10</v>
       </c>
-      <c r="D48" s="13">
+      <c r="D48">
         <v>200</v>
       </c>
-      <c r="E48" s="13">
+      <c r="E48">
         <v>230</v>
       </c>
       <c r="F48" s="4" t="s">
@@ -1526,16 +1522,16 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A49" s="13" t="s">
+      <c r="A49" t="s">
         <v>12</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C49" s="13" t="s">
+      <c r="C49" t="s">
         <v>11</v>
       </c>
-      <c r="E49" s="13">
+      <c r="E49">
         <v>200</v>
       </c>
       <c r="F49" s="4" t="s">
@@ -1543,16 +1539,16 @@
       </c>
     </row>
     <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="13" t="s">
+      <c r="A50" t="s">
         <v>6</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C50" s="13" t="s">
+      <c r="C50" t="s">
         <v>8</v>
       </c>
-      <c r="D50" s="13">
+      <c r="D50">
         <v>200</v>
       </c>
       <c r="F50" s="4" t="s">
@@ -1560,19 +1556,19 @@
       </c>
     </row>
     <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="13" t="s">
+      <c r="A51" t="s">
         <v>6</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C51" s="13" t="s">
+      <c r="C51" t="s">
         <v>9</v>
       </c>
-      <c r="D51" s="13">
+      <c r="D51">
         <v>130</v>
       </c>
-      <c r="E51" s="13">
+      <c r="E51">
         <v>200</v>
       </c>
       <c r="F51" s="4" t="s">
@@ -1580,19 +1576,19 @@
       </c>
     </row>
     <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="13" t="s">
+      <c r="A52" t="s">
         <v>6</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="13" t="s">
+      <c r="C52" t="s">
         <v>10</v>
       </c>
-      <c r="D52" s="13">
+      <c r="D52">
         <v>100</v>
       </c>
-      <c r="E52" s="13">
+      <c r="E52">
         <v>130</v>
       </c>
       <c r="F52" s="4" t="s">
@@ -1600,16 +1596,16 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A53" s="13" t="s">
+      <c r="A53" t="s">
         <v>6</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C53" s="13" t="s">
+      <c r="C53" t="s">
         <v>11</v>
       </c>
-      <c r="E53" s="13">
+      <c r="E53">
         <v>100</v>
       </c>
       <c r="F53" s="4" t="s">
@@ -1617,16 +1613,16 @@
       </c>
     </row>
     <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="13" t="s">
+      <c r="A54" t="s">
         <v>6</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C54" s="13" t="s">
+      <c r="C54" t="s">
         <v>8</v>
       </c>
-      <c r="D54" s="13">
+      <c r="D54">
         <v>260</v>
       </c>
       <c r="F54" s="4" t="s">
@@ -1634,19 +1630,19 @@
       </c>
     </row>
     <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="13" t="s">
+      <c r="A55" t="s">
         <v>6</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C55" s="13" t="s">
+      <c r="C55" t="s">
         <v>9</v>
       </c>
-      <c r="D55" s="13">
+      <c r="D55">
         <v>190</v>
       </c>
-      <c r="E55" s="13">
+      <c r="E55">
         <v>260</v>
       </c>
       <c r="F55" s="4" t="s">
@@ -1654,19 +1650,19 @@
       </c>
     </row>
     <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="13" t="s">
+      <c r="A56" t="s">
         <v>6</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C56" s="13" t="s">
+      <c r="C56" t="s">
         <v>10</v>
       </c>
-      <c r="D56" s="13">
+      <c r="D56">
         <v>160</v>
       </c>
-      <c r="E56" s="13">
+      <c r="E56">
         <v>190</v>
       </c>
       <c r="F56" s="4" t="s">
@@ -1674,16 +1670,16 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A57" s="13" t="s">
+      <c r="A57" t="s">
         <v>6</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C57" s="13" t="s">
+      <c r="C57" t="s">
         <v>11</v>
       </c>
-      <c r="E57" s="13">
+      <c r="E57">
         <v>160</v>
       </c>
       <c r="F57" s="4" t="s">
@@ -1691,16 +1687,16 @@
       </c>
     </row>
     <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="13" t="s">
+      <c r="A58" t="s">
         <v>6</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C58" s="13" t="s">
+      <c r="C58" t="s">
         <v>14</v>
       </c>
-      <c r="E58" s="13">
+      <c r="E58">
         <v>8.9</v>
       </c>
       <c r="F58" s="4" t="s">
@@ -1708,19 +1704,19 @@
       </c>
     </row>
     <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="13" t="s">
+      <c r="A59" t="s">
         <v>6</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C59" s="13" t="s">
+      <c r="C59" t="s">
         <v>16</v>
       </c>
-      <c r="D59" s="13">
+      <c r="D59">
         <v>8.9</v>
       </c>
-      <c r="E59" s="13">
+      <c r="E59">
         <v>10.199999999999999</v>
       </c>
       <c r="F59" s="4" t="s">
@@ -1728,16 +1724,16 @@
       </c>
     </row>
     <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="13" t="s">
+      <c r="A60" t="s">
         <v>6</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C60" s="13" t="s">
+      <c r="C60" t="s">
         <v>14</v>
       </c>
-      <c r="E60" s="13">
+      <c r="E60">
         <v>8.9</v>
       </c>
       <c r="F60" s="4" t="s">
@@ -1745,19 +1741,19 @@
       </c>
     </row>
     <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="13" t="s">
+      <c r="A61" t="s">
         <v>6</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C61" s="13" t="s">
+      <c r="C61" t="s">
         <v>16</v>
       </c>
-      <c r="D61" s="13">
+      <c r="D61">
         <v>8.9</v>
       </c>
-      <c r="E61" s="13">
+      <c r="E61">
         <v>10.199999999999999</v>
       </c>
       <c r="F61" s="4" t="s">
@@ -1765,16 +1761,16 @@
       </c>
     </row>
     <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="13" t="s">
+      <c r="A62" t="s">
         <v>12</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C62" s="13" t="s">
+      <c r="C62" t="s">
         <v>14</v>
       </c>
-      <c r="E62" s="13">
+      <c r="E62">
         <v>8.9</v>
       </c>
       <c r="F62" s="4" t="s">
@@ -1782,19 +1778,19 @@
       </c>
     </row>
     <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="13" t="s">
+      <c r="A63" t="s">
         <v>12</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C63" s="13" t="s">
+      <c r="C63" t="s">
         <v>16</v>
       </c>
-      <c r="D63" s="13">
+      <c r="D63">
         <v>8.9</v>
       </c>
-      <c r="E63" s="13">
+      <c r="E63">
         <v>10.199999999999999</v>
       </c>
       <c r="F63" s="4" t="s">
@@ -1802,16 +1798,16 @@
       </c>
     </row>
     <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="13" t="s">
+      <c r="A64" t="s">
         <v>12</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C64" s="13" t="s">
+      <c r="C64" t="s">
         <v>14</v>
       </c>
-      <c r="E64" s="13">
+      <c r="E64">
         <v>8.9</v>
       </c>
       <c r="F64" s="4" t="s">
@@ -1819,169 +1815,169 @@
       </c>
     </row>
     <row r="65" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="13" t="s">
+      <c r="A65" t="s">
         <v>12</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C65" s="13" t="s">
+      <c r="C65" t="s">
         <v>16</v>
       </c>
-      <c r="D65" s="13">
+      <c r="D65">
         <v>8.9</v>
       </c>
-      <c r="E65" s="13">
+      <c r="E65">
         <v>10.199999999999999</v>
       </c>
       <c r="F65" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="66" spans="1:6" s="17" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="13" t="s">
+    <row r="66" spans="1:6" s="15" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
         <v>6</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C66" s="13" t="s">
+      <c r="C66" t="s">
         <v>11</v>
       </c>
-      <c r="D66" s="13">
+      <c r="D66">
         <v>10.199999999999999</v>
       </c>
-      <c r="E66" s="13"/>
+      <c r="E66"/>
       <c r="F66" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="67" spans="1:6" s="17" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="13" t="s">
+    <row r="67" spans="1:6" s="15" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
         <v>6</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C67" s="13" t="s">
+      <c r="C67" t="s">
         <v>11</v>
       </c>
-      <c r="D67" s="13">
+      <c r="D67">
         <v>10.199999999999999</v>
       </c>
-      <c r="E67" s="13"/>
+      <c r="E67"/>
       <c r="F67" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="68" spans="1:6" s="17" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="13" t="s">
+    <row r="68" spans="1:6" s="15" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
         <v>12</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C68" s="13" t="s">
+      <c r="C68" t="s">
         <v>11</v>
       </c>
-      <c r="D68" s="13">
+      <c r="D68">
         <v>10.199999999999999</v>
       </c>
-      <c r="E68" s="13"/>
+      <c r="E68"/>
       <c r="F68" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="69" spans="1:6" s="17" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="13" t="s">
+    <row r="69" spans="1:6" s="15" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
         <v>12</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C69" s="13" t="s">
+      <c r="C69" t="s">
         <v>11</v>
       </c>
-      <c r="D69" s="13">
+      <c r="D69">
         <v>10.199999999999999</v>
       </c>
-      <c r="E69" s="13"/>
+      <c r="E69"/>
       <c r="F69" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="70" spans="1:6" s="17" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="13" t="s">
+    <row r="70" spans="1:6" s="15" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
         <v>6</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C70" s="13" t="s">
+      <c r="C70" t="s">
         <v>17</v>
       </c>
-      <c r="D70" s="13">
+      <c r="D70">
         <v>5300</v>
       </c>
-      <c r="E70" s="13"/>
+      <c r="E70"/>
       <c r="F70" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="71" spans="1:6" s="17" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="13" t="s">
+    <row r="71" spans="1:6" s="15" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
         <v>6</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C71" s="13" t="s">
+      <c r="C71" t="s">
         <v>18</v>
       </c>
-      <c r="D71" s="13">
+      <c r="D71">
         <v>5015</v>
       </c>
-      <c r="E71" s="13">
+      <c r="E71">
         <v>5300</v>
       </c>
       <c r="F71" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="72" spans="1:6" s="17" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="13" t="s">
+    <row r="72" spans="1:6" s="15" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
         <v>6</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C72" s="13" t="s">
+      <c r="C72" t="s">
         <v>11</v>
       </c>
-      <c r="D72" s="13">
+      <c r="D72">
         <v>4115</v>
       </c>
-      <c r="E72" s="13">
+      <c r="E72">
         <v>5015</v>
       </c>
       <c r="F72" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="73" spans="1:6" s="17" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="13" t="s">
+    <row r="73" spans="1:6" s="15" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
         <v>6</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C73" s="13" t="s">
+      <c r="C73" t="s">
         <v>19</v>
       </c>
-      <c r="D73" s="13">
+      <c r="D73">
         <v>3880</v>
       </c>
-      <c r="E73" s="13">
+      <c r="E73">
         <v>3900</v>
       </c>
       <c r="F73" s="4" t="s">
@@ -1989,16 +1985,16 @@
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A74" s="13" t="s">
+      <c r="A74" t="s">
         <v>6</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C74" s="13" t="s">
+      <c r="C74" t="s">
         <v>21</v>
       </c>
-      <c r="E74" s="13">
+      <c r="E74">
         <v>3880</v>
       </c>
       <c r="F74" s="4" t="s">
@@ -2006,16 +2002,16 @@
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A75" s="13" t="s">
+      <c r="A75" t="s">
         <v>6</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C75" s="13" t="s">
+      <c r="C75" t="s">
         <v>17</v>
       </c>
-      <c r="D75" s="13">
+      <c r="D75">
         <v>5300</v>
       </c>
       <c r="F75" s="4" t="s">
@@ -2023,19 +2019,19 @@
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A76" s="13" t="s">
+      <c r="A76" t="s">
         <v>6</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C76" s="13" t="s">
+      <c r="C76" t="s">
         <v>18</v>
       </c>
-      <c r="D76" s="13">
+      <c r="D76">
         <v>5015</v>
       </c>
-      <c r="E76" s="13">
+      <c r="E76">
         <v>5300</v>
       </c>
       <c r="F76" s="4" t="s">
@@ -2043,19 +2039,19 @@
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A77" s="13" t="s">
+      <c r="A77" t="s">
         <v>6</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C77" s="13" t="s">
+      <c r="C77" t="s">
         <v>11</v>
       </c>
-      <c r="D77" s="13">
+      <c r="D77">
         <v>4115</v>
       </c>
-      <c r="E77" s="13">
+      <c r="E77">
         <v>5015</v>
       </c>
       <c r="F77" s="5" t="s">
@@ -2063,19 +2059,19 @@
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A78" s="13" t="s">
+      <c r="A78" t="s">
         <v>6</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C78" s="13" t="s">
+      <c r="C78" t="s">
         <v>19</v>
       </c>
-      <c r="D78" s="13">
+      <c r="D78">
         <v>3880</v>
       </c>
-      <c r="E78" s="13">
+      <c r="E78">
         <v>3900</v>
       </c>
       <c r="F78" s="4" t="s">
@@ -2083,16 +2079,16 @@
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A79" s="13" t="s">
+      <c r="A79" t="s">
         <v>6</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C79" s="13" t="s">
+      <c r="C79" t="s">
         <v>21</v>
       </c>
-      <c r="E79" s="13">
+      <c r="E79">
         <v>3880</v>
       </c>
       <c r="F79" s="4" t="s">
@@ -2100,16 +2096,16 @@
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A80" s="13" t="s">
+      <c r="A80" t="s">
         <v>12</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C80" s="13" t="s">
+      <c r="C80" t="s">
         <v>17</v>
       </c>
-      <c r="D80" s="13">
+      <c r="D80">
         <v>5300</v>
       </c>
       <c r="F80" s="4" t="s">
@@ -2117,19 +2113,19 @@
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A81" s="13" t="s">
+      <c r="A81" t="s">
         <v>12</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C81" s="13" t="s">
+      <c r="C81" t="s">
         <v>18</v>
       </c>
-      <c r="D81" s="13">
+      <c r="D81">
         <v>5015</v>
       </c>
-      <c r="E81" s="13">
+      <c r="E81">
         <v>5300</v>
       </c>
       <c r="F81" s="4" t="s">
@@ -2137,19 +2133,19 @@
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A82" s="13" t="s">
+      <c r="A82" t="s">
         <v>12</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C82" s="13" t="s">
+      <c r="C82" t="s">
         <v>11</v>
       </c>
-      <c r="D82" s="13">
+      <c r="D82">
         <v>3915</v>
       </c>
-      <c r="E82" s="13">
+      <c r="E82">
         <v>5015</v>
       </c>
       <c r="F82" s="5" t="s">
@@ -2157,19 +2153,19 @@
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A83" s="13" t="s">
+      <c r="A83" t="s">
         <v>12</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C83" s="13" t="s">
+      <c r="C83" t="s">
         <v>19</v>
       </c>
-      <c r="D83" s="13">
+      <c r="D83">
         <v>3880</v>
       </c>
-      <c r="E83" s="13">
+      <c r="E83">
         <v>3900</v>
       </c>
       <c r="F83" s="4" t="s">
@@ -2177,16 +2173,16 @@
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A84" s="13" t="s">
+      <c r="A84" t="s">
         <v>12</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C84" s="13" t="s">
+      <c r="C84" t="s">
         <v>21</v>
       </c>
-      <c r="E84" s="13">
+      <c r="E84">
         <v>3880</v>
       </c>
       <c r="F84" s="4" t="s">
@@ -2194,16 +2190,16 @@
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A85" s="13" t="s">
+      <c r="A85" t="s">
         <v>12</v>
       </c>
       <c r="B85" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C85" s="13" t="s">
+      <c r="C85" t="s">
         <v>17</v>
       </c>
-      <c r="D85" s="13">
+      <c r="D85">
         <v>5300</v>
       </c>
       <c r="F85" s="4" t="s">
@@ -2211,19 +2207,19 @@
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A86" s="13" t="s">
+      <c r="A86" t="s">
         <v>12</v>
       </c>
       <c r="B86" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C86" s="13" t="s">
+      <c r="C86" t="s">
         <v>18</v>
       </c>
-      <c r="D86" s="13">
+      <c r="D86">
         <v>5015</v>
       </c>
-      <c r="E86" s="13">
+      <c r="E86">
         <v>5300</v>
       </c>
       <c r="F86" s="4" t="s">
@@ -2231,19 +2227,19 @@
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A87" s="13" t="s">
+      <c r="A87" t="s">
         <v>12</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C87" s="13" t="s">
+      <c r="C87" t="s">
         <v>11</v>
       </c>
-      <c r="D87" s="13">
+      <c r="D87">
         <v>3915</v>
       </c>
-      <c r="E87" s="13">
+      <c r="E87">
         <v>5015</v>
       </c>
       <c r="F87" s="5" t="s">
@@ -2251,19 +2247,19 @@
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A88" s="13" t="s">
+      <c r="A88" t="s">
         <v>12</v>
       </c>
       <c r="B88" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C88" s="13" t="s">
+      <c r="C88" t="s">
         <v>19</v>
       </c>
-      <c r="D88" s="13">
+      <c r="D88">
         <v>3880</v>
       </c>
-      <c r="E88" s="13">
+      <c r="E88">
         <v>3900</v>
       </c>
       <c r="F88" s="4" t="s">
@@ -2271,16 +2267,16 @@
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A89" s="13" t="s">
+      <c r="A89" t="s">
         <v>12</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C89" s="13" t="s">
+      <c r="C89" t="s">
         <v>21</v>
       </c>
-      <c r="E89" s="13">
+      <c r="E89">
         <v>3880</v>
       </c>
       <c r="F89" s="4" t="s">
@@ -2331,10 +2327,10 @@
       <c r="A2" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="9">
+      <c r="B2" s="5">
         <v>97</v>
       </c>
-      <c r="C2" s="9">
+      <c r="C2" s="5">
         <v>97.261899999999997</v>
       </c>
     </row>
@@ -10012,7 +10008,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A406477-0BDC-404F-93CF-7E7D1F43F43F}">
-  <dimension ref="A1:C547"/>
+  <dimension ref="A1:C544"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.54296875" customWidth="1"/>
@@ -10036,10 +10032,10 @@
       <c r="A2" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="9">
+      <c r="B2" s="5">
         <v>97</v>
       </c>
-      <c r="C2" s="9">
+      <c r="C2" s="5">
         <v>97.780900000000003</v>
       </c>
     </row>
@@ -10392,7 +10388,7 @@
         <v>97.891100000000009</v>
       </c>
       <c r="C34" s="5">
-        <v>97.890900000000002</v>
+        <v>97.891900000000007</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
@@ -10400,10 +10396,10 @@
         <v>27</v>
       </c>
       <c r="B35" s="4">
-        <v>97.891000000000005</v>
+        <v>97.891999999999996</v>
       </c>
       <c r="C35" s="4">
-        <v>97.891000000000005</v>
+        <v>97.891999999999996</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
@@ -10411,7 +10407,7 @@
         <v>28</v>
       </c>
       <c r="B36" s="5">
-        <v>97.891100000000009</v>
+        <v>97.892099999999999</v>
       </c>
       <c r="C36" s="5">
         <v>97.899900000000002</v>
@@ -10920,7 +10916,7 @@
         <v>98.120100000000008</v>
       </c>
       <c r="C82" s="5">
-        <v>98.116900000000001</v>
+        <v>98.126900000000006</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.35">
@@ -12350,3691 +12346,3658 @@
         <v>98.709100000000007</v>
       </c>
       <c r="C212" s="5">
-        <v>98.7059</v>
+        <v>98.709900000000005</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>27</v>
-      </c>
-      <c r="B213" s="4">
-        <v>98.706000000000003</v>
-      </c>
-      <c r="C213" s="4">
-        <v>98.706000000000003</v>
+        <v>28</v>
+      </c>
+      <c r="B213" s="5">
+        <v>98.71</v>
+      </c>
+      <c r="C213" s="5">
+        <v>98.713899999999995</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>28</v>
-      </c>
-      <c r="B214" s="5">
-        <v>98.706100000000006</v>
-      </c>
-      <c r="C214" s="5">
-        <v>98.707899999999995</v>
+        <v>27</v>
+      </c>
+      <c r="B214" s="4">
+        <v>98.713999999999999</v>
+      </c>
+      <c r="C214" s="4">
+        <v>98.713999999999999</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>27</v>
-      </c>
-      <c r="B215" s="4">
-        <v>98.707999999999998</v>
-      </c>
-      <c r="C215" s="4">
-        <v>98.707999999999998</v>
+        <v>28</v>
+      </c>
+      <c r="B215" s="5">
+        <v>98.714100000000002</v>
+      </c>
+      <c r="C215" s="5">
+        <v>98.721899999999991</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>28</v>
-      </c>
-      <c r="B216" s="5">
-        <v>98.708100000000002</v>
-      </c>
-      <c r="C216" s="5">
-        <v>98.713899999999995</v>
+        <v>27</v>
+      </c>
+      <c r="B216" s="4">
+        <v>98.721999999999994</v>
+      </c>
+      <c r="C216" s="4">
+        <v>98.721999999999994</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>27</v>
-      </c>
-      <c r="B217" s="4">
-        <v>98.713999999999999</v>
-      </c>
-      <c r="C217" s="4">
-        <v>98.713999999999999</v>
+        <v>28</v>
+      </c>
+      <c r="B217" s="5">
+        <v>98.722099999999998</v>
+      </c>
+      <c r="C217" s="5">
+        <v>98.730899999999991</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>28</v>
-      </c>
-      <c r="B218" s="5">
-        <v>98.714100000000002</v>
-      </c>
-      <c r="C218" s="5">
-        <v>98.721899999999991</v>
+        <v>27</v>
+      </c>
+      <c r="B218" s="4">
+        <v>98.730999999999995</v>
+      </c>
+      <c r="C218" s="4">
+        <v>98.730999999999995</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>27</v>
-      </c>
-      <c r="B219" s="4">
-        <v>98.721999999999994</v>
-      </c>
-      <c r="C219" s="4">
-        <v>98.721999999999994</v>
+        <v>28</v>
+      </c>
+      <c r="B219" s="5">
+        <v>98.731099999999998</v>
+      </c>
+      <c r="C219" s="5">
+        <v>98.738900000000001</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>28</v>
-      </c>
-      <c r="B220" s="5">
-        <v>98.722099999999998</v>
-      </c>
-      <c r="C220" s="5">
-        <v>98.730899999999991</v>
+        <v>27</v>
+      </c>
+      <c r="B220" s="4">
+        <v>98.739000000000004</v>
+      </c>
+      <c r="C220" s="4">
+        <v>98.739000000000004</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>27</v>
-      </c>
-      <c r="B221" s="4">
-        <v>98.730999999999995</v>
-      </c>
-      <c r="C221" s="4">
-        <v>98.730999999999995</v>
+        <v>28</v>
+      </c>
+      <c r="B221" s="5">
+        <v>98.739100000000008</v>
+      </c>
+      <c r="C221" s="5">
+        <v>98.748899999999992</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>28</v>
-      </c>
-      <c r="B222" s="5">
-        <v>98.731099999999998</v>
-      </c>
-      <c r="C222" s="5">
-        <v>98.738900000000001</v>
+        <v>27</v>
+      </c>
+      <c r="B222" s="4">
+        <v>98.748999999999995</v>
+      </c>
+      <c r="C222" s="4">
+        <v>98.748999999999995</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>27</v>
-      </c>
-      <c r="B223" s="4">
-        <v>98.739000000000004</v>
-      </c>
-      <c r="C223" s="4">
-        <v>98.739000000000004</v>
+        <v>28</v>
+      </c>
+      <c r="B223" s="5">
+        <v>98.749099999999999</v>
+      </c>
+      <c r="C223" s="5">
+        <v>98.760899999999992</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>28</v>
-      </c>
-      <c r="B224" s="5">
-        <v>98.739100000000008</v>
-      </c>
-      <c r="C224" s="5">
-        <v>98.748899999999992</v>
+        <v>27</v>
+      </c>
+      <c r="B224" s="4">
+        <v>98.760999999999996</v>
+      </c>
+      <c r="C224" s="4">
+        <v>98.760999999999996</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>27</v>
-      </c>
-      <c r="B225" s="4">
-        <v>98.748999999999995</v>
-      </c>
-      <c r="C225" s="4">
-        <v>98.748999999999995</v>
+        <v>28</v>
+      </c>
+      <c r="B225" s="5">
+        <v>98.761099999999999</v>
+      </c>
+      <c r="C225" s="5">
+        <v>98.770899999999997</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>28</v>
-      </c>
-      <c r="B226" s="5">
-        <v>98.749099999999999</v>
-      </c>
-      <c r="C226" s="5">
-        <v>98.760899999999992</v>
+        <v>27</v>
+      </c>
+      <c r="B226" s="4">
+        <v>98.771000000000001</v>
+      </c>
+      <c r="C226" s="4">
+        <v>98.771000000000001</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>27</v>
-      </c>
-      <c r="B227" s="4">
-        <v>98.760999999999996</v>
-      </c>
-      <c r="C227" s="4">
-        <v>98.760999999999996</v>
+        <v>28</v>
+      </c>
+      <c r="B227" s="5">
+        <v>98.771100000000004</v>
+      </c>
+      <c r="C227" s="5">
+        <v>98.773899999999998</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>28</v>
-      </c>
-      <c r="B228" s="5">
-        <v>98.761099999999999</v>
-      </c>
-      <c r="C228" s="5">
-        <v>98.770899999999997</v>
+        <v>27</v>
+      </c>
+      <c r="B228" s="4">
+        <v>98.774000000000001</v>
+      </c>
+      <c r="C228" s="4">
+        <v>98.774000000000001</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>27</v>
-      </c>
-      <c r="B229" s="4">
-        <v>98.771000000000001</v>
-      </c>
-      <c r="C229" s="4">
-        <v>98.771000000000001</v>
+        <v>28</v>
+      </c>
+      <c r="B229" s="5">
+        <v>98.774100000000004</v>
+      </c>
+      <c r="C229" s="5">
+        <v>98.794899999999998</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>28</v>
-      </c>
-      <c r="B230" s="5">
-        <v>98.771100000000004</v>
-      </c>
-      <c r="C230" s="5">
-        <v>98.753900000000002</v>
+        <v>27</v>
+      </c>
+      <c r="B230" s="4">
+        <v>98.795000000000002</v>
+      </c>
+      <c r="C230" s="4">
+        <v>98.795000000000002</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>27</v>
-      </c>
-      <c r="B231" s="4">
-        <v>98.754000000000005</v>
-      </c>
-      <c r="C231" s="4">
-        <v>98.754000000000005</v>
+        <v>28</v>
+      </c>
+      <c r="B231" s="5">
+        <v>98.795100000000005</v>
+      </c>
+      <c r="C231" s="5">
+        <v>98.806899999999999</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>28</v>
-      </c>
-      <c r="B232" s="5">
-        <v>98.754100000000008</v>
-      </c>
-      <c r="C232" s="5">
-        <v>98.794899999999998</v>
+        <v>27</v>
+      </c>
+      <c r="B232" s="4">
+        <v>98.807000000000002</v>
+      </c>
+      <c r="C232" s="4">
+        <v>98.807000000000002</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>27</v>
-      </c>
-      <c r="B233" s="4">
-        <v>98.795000000000002</v>
-      </c>
-      <c r="C233" s="4">
-        <v>98.795000000000002</v>
+        <v>28</v>
+      </c>
+      <c r="B233" s="5">
+        <v>98.807100000000005</v>
+      </c>
+      <c r="C233" s="5">
+        <v>98.817899999999995</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>28</v>
-      </c>
-      <c r="B234" s="5">
-        <v>98.795100000000005</v>
-      </c>
-      <c r="C234" s="5">
-        <v>98.806899999999999</v>
+        <v>27</v>
+      </c>
+      <c r="B234" s="4">
+        <v>98.817999999999998</v>
+      </c>
+      <c r="C234" s="4">
+        <v>98.817999999999998</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>27</v>
-      </c>
-      <c r="B235" s="4">
-        <v>98.807000000000002</v>
-      </c>
-      <c r="C235" s="4">
-        <v>98.807000000000002</v>
+        <v>28</v>
+      </c>
+      <c r="B235" s="5">
+        <v>98.818100000000001</v>
+      </c>
+      <c r="C235" s="5">
+        <v>98.82889999999999</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>28</v>
-      </c>
-      <c r="B236" s="5">
-        <v>98.807100000000005</v>
-      </c>
-      <c r="C236" s="5">
-        <v>98.817899999999995</v>
+        <v>27</v>
+      </c>
+      <c r="B236" s="4">
+        <v>98.828999999999994</v>
+      </c>
+      <c r="C236" s="4">
+        <v>98.828999999999994</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>27</v>
-      </c>
-      <c r="B237" s="4">
-        <v>98.817999999999998</v>
-      </c>
-      <c r="C237" s="4">
-        <v>98.817999999999998</v>
+        <v>28</v>
+      </c>
+      <c r="B237" s="5">
+        <v>98.829099999999997</v>
+      </c>
+      <c r="C237" s="5">
+        <v>98.8399</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>28</v>
-      </c>
-      <c r="B238" s="5">
-        <v>98.818100000000001</v>
-      </c>
-      <c r="C238" s="5">
-        <v>98.82889999999999</v>
+        <v>27</v>
+      </c>
+      <c r="B238" s="4">
+        <v>98.84</v>
+      </c>
+      <c r="C238" s="4">
+        <v>98.84</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>27</v>
-      </c>
-      <c r="B239" s="4">
-        <v>98.828999999999994</v>
-      </c>
-      <c r="C239" s="4">
-        <v>98.828999999999994</v>
+        <v>28</v>
+      </c>
+      <c r="B239" s="5">
+        <v>98.840100000000007</v>
+      </c>
+      <c r="C239" s="5">
+        <v>98.850899999999996</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>28</v>
-      </c>
-      <c r="B240" s="5">
-        <v>98.829099999999997</v>
-      </c>
-      <c r="C240" s="5">
-        <v>98.8399</v>
+        <v>27</v>
+      </c>
+      <c r="B240" s="4">
+        <v>98.850999999999999</v>
+      </c>
+      <c r="C240" s="4">
+        <v>98.850999999999999</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>27</v>
-      </c>
-      <c r="B241" s="4">
-        <v>98.84</v>
-      </c>
-      <c r="C241" s="4">
-        <v>98.84</v>
+        <v>28</v>
+      </c>
+      <c r="B241" s="5">
+        <v>98.851100000000002</v>
+      </c>
+      <c r="C241" s="5">
+        <v>98.861899999999991</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>28</v>
-      </c>
-      <c r="B242" s="5">
-        <v>98.840100000000007</v>
-      </c>
-      <c r="C242" s="5">
-        <v>98.850899999999996</v>
+        <v>27</v>
+      </c>
+      <c r="B242" s="4">
+        <v>98.861999999999995</v>
+      </c>
+      <c r="C242" s="4">
+        <v>98.861999999999995</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>27</v>
-      </c>
-      <c r="B243" s="4">
-        <v>98.850999999999999</v>
-      </c>
-      <c r="C243" s="4">
-        <v>98.850999999999999</v>
+        <v>28</v>
+      </c>
+      <c r="B243" s="5">
+        <v>98.862099999999998</v>
+      </c>
+      <c r="C243" s="5">
+        <v>98.873899999999992</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>28</v>
-      </c>
-      <c r="B244" s="5">
-        <v>98.851100000000002</v>
-      </c>
-      <c r="C244" s="5">
-        <v>98.861899999999991</v>
+        <v>27</v>
+      </c>
+      <c r="B244" s="4">
+        <v>98.873999999999995</v>
+      </c>
+      <c r="C244" s="4">
+        <v>98.873999999999995</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>27</v>
-      </c>
-      <c r="B245" s="4">
-        <v>98.861999999999995</v>
-      </c>
-      <c r="C245" s="4">
-        <v>98.861999999999995</v>
+        <v>28</v>
+      </c>
+      <c r="B245" s="5">
+        <v>98.874099999999999</v>
+      </c>
+      <c r="C245" s="5">
+        <v>98.884900000000002</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>28</v>
-      </c>
-      <c r="B246" s="5">
-        <v>98.862099999999998</v>
-      </c>
-      <c r="C246" s="5">
-        <v>98.873899999999992</v>
+        <v>27</v>
+      </c>
+      <c r="B246" s="4">
+        <v>98.885000000000005</v>
+      </c>
+      <c r="C246" s="4">
+        <v>98.885000000000005</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>27</v>
-      </c>
-      <c r="B247" s="4">
-        <v>98.873999999999995</v>
-      </c>
-      <c r="C247" s="4">
-        <v>98.873999999999995</v>
+        <v>28</v>
+      </c>
+      <c r="B247" s="5">
+        <v>98.885100000000008</v>
+      </c>
+      <c r="C247" s="5">
+        <v>98.896900000000002</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>28</v>
-      </c>
-      <c r="B248" s="5">
-        <v>98.874099999999999</v>
-      </c>
-      <c r="C248" s="5">
-        <v>98.884900000000002</v>
+        <v>27</v>
+      </c>
+      <c r="B248" s="4">
+        <v>98.897000000000006</v>
+      </c>
+      <c r="C248" s="4">
+        <v>98.897000000000006</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>27</v>
-      </c>
-      <c r="B249" s="4">
-        <v>98.885000000000005</v>
-      </c>
-      <c r="C249" s="4">
-        <v>98.885000000000005</v>
+        <v>28</v>
+      </c>
+      <c r="B249" s="5">
+        <v>98.897100000000009</v>
+      </c>
+      <c r="C249" s="5">
+        <v>98.906899999999993</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>28</v>
-      </c>
-      <c r="B250" s="5">
-        <v>98.885100000000008</v>
-      </c>
-      <c r="C250" s="5">
-        <v>98.896900000000002</v>
+        <v>27</v>
+      </c>
+      <c r="B250" s="4">
+        <v>98.906999999999996</v>
+      </c>
+      <c r="C250" s="4">
+        <v>98.906999999999996</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>27</v>
-      </c>
-      <c r="B251" s="4">
-        <v>98.897000000000006</v>
-      </c>
-      <c r="C251" s="4">
-        <v>98.897000000000006</v>
+        <v>28</v>
+      </c>
+      <c r="B251" s="5">
+        <v>98.9071</v>
+      </c>
+      <c r="C251" s="5">
+        <v>98.913899999999998</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>28</v>
-      </c>
-      <c r="B252" s="5">
-        <v>98.897100000000009</v>
-      </c>
-      <c r="C252" s="5">
-        <v>98.906899999999993</v>
+        <v>27</v>
+      </c>
+      <c r="B252" s="4">
+        <v>98.914000000000001</v>
+      </c>
+      <c r="C252" s="4">
+        <v>98.914000000000001</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>27</v>
-      </c>
-      <c r="B253" s="4">
-        <v>98.906999999999996</v>
-      </c>
-      <c r="C253" s="4">
-        <v>98.906999999999996</v>
+        <v>28</v>
+      </c>
+      <c r="B253" s="5">
+        <v>98.914100000000005</v>
+      </c>
+      <c r="C253" s="5">
+        <v>98.920900000000003</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>28</v>
-      </c>
-      <c r="B254" s="5">
-        <v>98.9071</v>
-      </c>
-      <c r="C254" s="5">
-        <v>98.913899999999998</v>
+        <v>27</v>
+      </c>
+      <c r="B254" s="4">
+        <v>98.921000000000006</v>
+      </c>
+      <c r="C254" s="4">
+        <v>98.921000000000006</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>27</v>
-      </c>
-      <c r="B255" s="4">
-        <v>98.914000000000001</v>
-      </c>
-      <c r="C255" s="4">
-        <v>98.914000000000001</v>
+        <v>28</v>
+      </c>
+      <c r="B255" s="5">
+        <v>98.92110000000001</v>
+      </c>
+      <c r="C255" s="5">
+        <v>98.926900000000003</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>28</v>
-      </c>
-      <c r="B256" s="5">
-        <v>98.914100000000005</v>
-      </c>
-      <c r="C256" s="5">
-        <v>98.920900000000003</v>
+        <v>27</v>
+      </c>
+      <c r="B256" s="4">
+        <v>98.927000000000007</v>
+      </c>
+      <c r="C256" s="4">
+        <v>98.927000000000007</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>27</v>
-      </c>
-      <c r="B257" s="4">
-        <v>98.921000000000006</v>
-      </c>
-      <c r="C257" s="4">
-        <v>98.921000000000006</v>
+        <v>28</v>
+      </c>
+      <c r="B257" s="5">
+        <v>98.92710000000001</v>
+      </c>
+      <c r="C257" s="5">
+        <v>98.929900000000004</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>28</v>
-      </c>
-      <c r="B258" s="5">
-        <v>98.92110000000001</v>
-      </c>
-      <c r="C258" s="5">
-        <v>98.926900000000003</v>
+        <v>27</v>
+      </c>
+      <c r="B258" s="4">
+        <v>98.93</v>
+      </c>
+      <c r="C258" s="4">
+        <v>98.93</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>27</v>
-      </c>
-      <c r="B259" s="4">
-        <v>98.927000000000007</v>
-      </c>
-      <c r="C259" s="4">
-        <v>98.927000000000007</v>
+        <v>28</v>
+      </c>
+      <c r="B259" s="5">
+        <v>98.93010000000001</v>
+      </c>
+      <c r="C259" s="5">
+        <v>98.937899999999999</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>28</v>
-      </c>
-      <c r="B260" s="5">
-        <v>98.92710000000001</v>
-      </c>
-      <c r="C260" s="5">
-        <v>98.929900000000004</v>
+        <v>27</v>
+      </c>
+      <c r="B260" s="4">
+        <v>98.938000000000002</v>
+      </c>
+      <c r="C260" s="4">
+        <v>98.938000000000002</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>27</v>
-      </c>
-      <c r="B261" s="4">
-        <v>98.93</v>
-      </c>
-      <c r="C261" s="4">
-        <v>98.93</v>
+        <v>28</v>
+      </c>
+      <c r="B261" s="5">
+        <v>98.938100000000006</v>
+      </c>
+      <c r="C261" s="5">
+        <v>98.943899999999999</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>28</v>
-      </c>
-      <c r="B262" s="5">
-        <v>98.93010000000001</v>
-      </c>
-      <c r="C262" s="5">
-        <v>98.937899999999999</v>
+        <v>27</v>
+      </c>
+      <c r="B262" s="4">
+        <v>98.944000000000003</v>
+      </c>
+      <c r="C262" s="4">
+        <v>98.944000000000003</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>27</v>
-      </c>
-      <c r="B263" s="4">
-        <v>98.938000000000002</v>
-      </c>
-      <c r="C263" s="4">
-        <v>98.938000000000002</v>
+        <v>28</v>
+      </c>
+      <c r="B263" s="5">
+        <v>98.944100000000006</v>
+      </c>
+      <c r="C263" s="5">
+        <v>98.95389999999999</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>28</v>
-      </c>
-      <c r="B264" s="5">
-        <v>98.938100000000006</v>
-      </c>
-      <c r="C264" s="5">
-        <v>98.943899999999999</v>
+        <v>27</v>
+      </c>
+      <c r="B264" s="4">
+        <v>98.953999999999994</v>
+      </c>
+      <c r="C264" s="4">
+        <v>98.953999999999994</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>27</v>
-      </c>
-      <c r="B265" s="4">
-        <v>98.944000000000003</v>
-      </c>
-      <c r="C265" s="4">
-        <v>98.944000000000003</v>
+        <v>28</v>
+      </c>
+      <c r="B265" s="5">
+        <v>98.954099999999997</v>
+      </c>
+      <c r="C265" s="5">
+        <v>98.963899999999995</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>28</v>
-      </c>
-      <c r="B266" s="5">
-        <v>98.944100000000006</v>
-      </c>
-      <c r="C266" s="5">
-        <v>98.95389999999999</v>
+        <v>27</v>
+      </c>
+      <c r="B266" s="4">
+        <v>98.963999999999999</v>
+      </c>
+      <c r="C266" s="4">
+        <v>98.963999999999999</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>27</v>
-      </c>
-      <c r="B267" s="4">
-        <v>98.953999999999994</v>
-      </c>
-      <c r="C267" s="4">
-        <v>98.953999999999994</v>
+        <v>28</v>
+      </c>
+      <c r="B267" s="5">
+        <v>98.964100000000002</v>
+      </c>
+      <c r="C267" s="5">
+        <v>98.9739</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>28</v>
-      </c>
-      <c r="B268" s="5">
-        <v>98.954099999999997</v>
-      </c>
-      <c r="C268" s="5">
-        <v>98.963899999999995</v>
+        <v>27</v>
+      </c>
+      <c r="B268" s="4">
+        <v>98.974000000000004</v>
+      </c>
+      <c r="C268" s="4">
+        <v>98.974000000000004</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>27</v>
-      </c>
-      <c r="B269" s="4">
-        <v>98.963999999999999</v>
-      </c>
-      <c r="C269" s="4">
-        <v>98.963999999999999</v>
+        <v>28</v>
+      </c>
+      <c r="B269" s="5">
+        <v>98.974100000000007</v>
+      </c>
+      <c r="C269" s="5">
+        <v>98.983899999999991</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>28</v>
-      </c>
-      <c r="B270" s="5">
-        <v>98.964100000000002</v>
-      </c>
-      <c r="C270" s="5">
-        <v>98.9739</v>
+        <v>27</v>
+      </c>
+      <c r="B270" s="4">
+        <v>98.983999999999995</v>
+      </c>
+      <c r="C270" s="4">
+        <v>98.983999999999995</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>27</v>
-      </c>
-      <c r="B271" s="4">
-        <v>98.974000000000004</v>
-      </c>
-      <c r="C271" s="4">
-        <v>98.974000000000004</v>
+        <v>28</v>
+      </c>
+      <c r="B271" s="5">
+        <v>98.984099999999998</v>
+      </c>
+      <c r="C271" s="5">
+        <v>98.993899999999996</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>28</v>
-      </c>
-      <c r="B272" s="5">
-        <v>98.974100000000007</v>
-      </c>
-      <c r="C272" s="5">
-        <v>98.983899999999991</v>
+        <v>27</v>
+      </c>
+      <c r="B272" s="4">
+        <v>98.994</v>
+      </c>
+      <c r="C272" s="4">
+        <v>98.994</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>27</v>
-      </c>
-      <c r="B273" s="4">
-        <v>98.983999999999995</v>
-      </c>
-      <c r="C273" s="4">
-        <v>98.983999999999995</v>
+        <v>28</v>
+      </c>
+      <c r="B273" s="5">
+        <v>98.994100000000003</v>
+      </c>
+      <c r="C273" s="5">
+        <v>99.003899999999902</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>28</v>
-      </c>
-      <c r="B274" s="5">
-        <v>98.984099999999998</v>
-      </c>
-      <c r="C274" s="5">
-        <v>98.993899999999996</v>
+        <v>27</v>
+      </c>
+      <c r="B274" s="4">
+        <v>99.003999999999905</v>
+      </c>
+      <c r="C274" s="4">
+        <v>99.003999999999905</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>27</v>
-      </c>
-      <c r="B275" s="4">
-        <v>98.994</v>
-      </c>
-      <c r="C275" s="4">
-        <v>98.994</v>
+        <v>28</v>
+      </c>
+      <c r="B275" s="5">
+        <v>99.004099999999909</v>
+      </c>
+      <c r="C275" s="5">
+        <v>99.013899999999893</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>28</v>
-      </c>
-      <c r="B276" s="5">
-        <v>98.994100000000003</v>
-      </c>
-      <c r="C276" s="5">
-        <v>99.003899999999902</v>
+        <v>27</v>
+      </c>
+      <c r="B276" s="4">
+        <v>99.013999999999896</v>
+      </c>
+      <c r="C276" s="4">
+        <v>99.013999999999896</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>27</v>
-      </c>
-      <c r="B277" s="4">
-        <v>99.003999999999905</v>
-      </c>
-      <c r="C277" s="4">
-        <v>99.003999999999905</v>
+        <v>28</v>
+      </c>
+      <c r="B277" s="5">
+        <v>99.0140999999999</v>
+      </c>
+      <c r="C277" s="5">
+        <v>99.023899999999898</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>28</v>
-      </c>
-      <c r="B278" s="5">
-        <v>99.004099999999909</v>
-      </c>
-      <c r="C278" s="5">
-        <v>99.013899999999893</v>
+        <v>27</v>
+      </c>
+      <c r="B278" s="4">
+        <v>99.023999999999901</v>
+      </c>
+      <c r="C278" s="4">
+        <v>99.023999999999901</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>27</v>
-      </c>
-      <c r="B279" s="4">
-        <v>99.013999999999896</v>
-      </c>
-      <c r="C279" s="4">
-        <v>99.013999999999896</v>
+        <v>28</v>
+      </c>
+      <c r="B279" s="5">
+        <v>99.024099999999905</v>
+      </c>
+      <c r="C279" s="5">
+        <v>99.033899999999903</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>28</v>
-      </c>
-      <c r="B280" s="5">
-        <v>99.0140999999999</v>
-      </c>
-      <c r="C280" s="5">
-        <v>99.023899999999898</v>
+        <v>27</v>
+      </c>
+      <c r="B280" s="4">
+        <v>99.033999999999907</v>
+      </c>
+      <c r="C280" s="4">
+        <v>99.033999999999907</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>27</v>
-      </c>
-      <c r="B281" s="4">
-        <v>99.023999999999901</v>
-      </c>
-      <c r="C281" s="4">
-        <v>99.023999999999901</v>
+        <v>28</v>
+      </c>
+      <c r="B281" s="5">
+        <v>99.03409999999991</v>
+      </c>
+      <c r="C281" s="5">
+        <v>99.043899999999894</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>28</v>
-      </c>
-      <c r="B282" s="5">
-        <v>99.024099999999905</v>
-      </c>
-      <c r="C282" s="5">
-        <v>99.033899999999903</v>
+        <v>27</v>
+      </c>
+      <c r="B282" s="4">
+        <v>99.043999999999897</v>
+      </c>
+      <c r="C282" s="4">
+        <v>99.043999999999897</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>27</v>
-      </c>
-      <c r="B283" s="4">
-        <v>99.033999999999907</v>
-      </c>
-      <c r="C283" s="4">
-        <v>99.033999999999907</v>
+        <v>28</v>
+      </c>
+      <c r="B283" s="5">
+        <v>99.044099999999901</v>
+      </c>
+      <c r="C283" s="5">
+        <v>99.053899999999899</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>28</v>
-      </c>
-      <c r="B284" s="5">
-        <v>99.03409999999991</v>
-      </c>
-      <c r="C284" s="5">
-        <v>99.043899999999894</v>
+        <v>27</v>
+      </c>
+      <c r="B284" s="4">
+        <v>99.053999999999903</v>
+      </c>
+      <c r="C284" s="4">
+        <v>99.053999999999903</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>27</v>
-      </c>
-      <c r="B285" s="4">
-        <v>99.043999999999897</v>
-      </c>
-      <c r="C285" s="4">
-        <v>99.043999999999897</v>
+        <v>28</v>
+      </c>
+      <c r="B285" s="5">
+        <v>99.054099999999906</v>
+      </c>
+      <c r="C285" s="5">
+        <v>99.062899999999999</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>28</v>
-      </c>
-      <c r="B286" s="5">
-        <v>99.044099999999901</v>
-      </c>
-      <c r="C286" s="5">
-        <v>99.053899999999899</v>
+        <v>27</v>
+      </c>
+      <c r="B286" s="4">
+        <v>99.063000000000002</v>
+      </c>
+      <c r="C286" s="4">
+        <v>99.063000000000002</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>27</v>
-      </c>
-      <c r="B287" s="4">
-        <v>99.053999999999903</v>
-      </c>
-      <c r="C287" s="4">
-        <v>99.053999999999903</v>
+        <v>28</v>
+      </c>
+      <c r="B287" s="5">
+        <v>99.063100000000006</v>
+      </c>
+      <c r="C287" s="5">
+        <v>99.07289999999999</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>28</v>
-      </c>
-      <c r="B288" s="5">
-        <v>99.054099999999906</v>
-      </c>
-      <c r="C288" s="5">
-        <v>99.062899999999999</v>
+        <v>27</v>
+      </c>
+      <c r="B288" s="4">
+        <v>99.072999999999993</v>
+      </c>
+      <c r="C288" s="4">
+        <v>99.072999999999993</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>27</v>
-      </c>
-      <c r="B289" s="4">
-        <v>99.063000000000002</v>
-      </c>
-      <c r="C289" s="4">
-        <v>99.063000000000002</v>
+        <v>28</v>
+      </c>
+      <c r="B289" s="5">
+        <v>99.073099999999997</v>
+      </c>
+      <c r="C289" s="5">
+        <v>99.082899999999995</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>28</v>
-      </c>
-      <c r="B290" s="5">
-        <v>99.063100000000006</v>
-      </c>
-      <c r="C290" s="5">
-        <v>99.07289999999999</v>
+        <v>27</v>
+      </c>
+      <c r="B290" s="4">
+        <v>99.082999999999998</v>
+      </c>
+      <c r="C290" s="4">
+        <v>99.082999999999998</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>27</v>
-      </c>
-      <c r="B291" s="4">
-        <v>99.072999999999993</v>
-      </c>
-      <c r="C291" s="4">
-        <v>99.072999999999993</v>
+        <v>28</v>
+      </c>
+      <c r="B291" s="5">
+        <v>99.083100000000002</v>
+      </c>
+      <c r="C291" s="5">
+        <v>99.0929</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>28</v>
-      </c>
-      <c r="B292" s="5">
-        <v>99.073099999999997</v>
-      </c>
-      <c r="C292" s="5">
-        <v>99.082899999999995</v>
+        <v>27</v>
+      </c>
+      <c r="B292" s="4">
+        <v>99.093000000000004</v>
+      </c>
+      <c r="C292" s="4">
+        <v>99.093000000000004</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>27</v>
-      </c>
-      <c r="B293" s="4">
-        <v>99.082999999999998</v>
-      </c>
-      <c r="C293" s="4">
-        <v>99.082999999999998</v>
+        <v>28</v>
+      </c>
+      <c r="B293" s="5">
+        <v>99.093100000000007</v>
+      </c>
+      <c r="C293" s="5">
+        <v>99.103899999999996</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>28</v>
-      </c>
-      <c r="B294" s="5">
-        <v>99.083100000000002</v>
-      </c>
-      <c r="C294" s="5">
-        <v>99.0929</v>
+        <v>27</v>
+      </c>
+      <c r="B294" s="4">
+        <v>99.103999999999999</v>
+      </c>
+      <c r="C294" s="4">
+        <v>99.103999999999999</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>27</v>
-      </c>
-      <c r="B295" s="4">
-        <v>99.093000000000004</v>
-      </c>
-      <c r="C295" s="4">
-        <v>99.093000000000004</v>
+        <v>28</v>
+      </c>
+      <c r="B295" s="5">
+        <v>99.104100000000003</v>
+      </c>
+      <c r="C295" s="5">
+        <v>99.115899999999996</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>28</v>
-      </c>
-      <c r="B296" s="5">
-        <v>99.093100000000007</v>
-      </c>
-      <c r="C296" s="5">
-        <v>99.103899999999996</v>
+        <v>27</v>
+      </c>
+      <c r="B296" s="4">
+        <v>99.116</v>
+      </c>
+      <c r="C296" s="4">
+        <v>99.116</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>27</v>
-      </c>
-      <c r="B297" s="4">
-        <v>99.103999999999999</v>
-      </c>
-      <c r="C297" s="4">
-        <v>99.103999999999999</v>
+        <v>28</v>
+      </c>
+      <c r="B297" s="5">
+        <v>99.116100000000003</v>
+      </c>
+      <c r="C297" s="5">
+        <v>99.125900000000001</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>28</v>
-      </c>
-      <c r="B298" s="5">
-        <v>99.104100000000003</v>
-      </c>
-      <c r="C298" s="5">
-        <v>99.115899999999996</v>
+        <v>27</v>
+      </c>
+      <c r="B298" s="4">
+        <v>99126</v>
+      </c>
+      <c r="C298" s="4">
+        <v>99126</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>27</v>
-      </c>
-      <c r="B299" s="4">
-        <v>99.116</v>
-      </c>
-      <c r="C299" s="4">
-        <v>99.116</v>
+        <v>28</v>
+      </c>
+      <c r="B299" s="5">
+        <v>99.126099999999994</v>
+      </c>
+      <c r="C299" s="5">
+        <v>99.136899999999997</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>28</v>
-      </c>
-      <c r="B300" s="5">
-        <v>99.116100000000003</v>
-      </c>
-      <c r="C300" s="5">
-        <v>99.125900000000001</v>
+        <v>27</v>
+      </c>
+      <c r="B300" s="4">
+        <v>99.137</v>
+      </c>
+      <c r="C300" s="4">
+        <v>99.137</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>27</v>
-      </c>
-      <c r="B301" s="4">
-        <v>99126</v>
-      </c>
-      <c r="C301" s="4">
-        <v>99126</v>
+        <v>28</v>
+      </c>
+      <c r="B301" s="5">
+        <v>99.137100000000004</v>
+      </c>
+      <c r="C301" s="5">
+        <v>99.147899999999993</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>28</v>
-      </c>
-      <c r="B302" s="5">
-        <v>99.126099999999994</v>
-      </c>
-      <c r="C302" s="5">
-        <v>99.136899999999997</v>
+        <v>27</v>
+      </c>
+      <c r="B302" s="4">
+        <v>99.147999999999996</v>
+      </c>
+      <c r="C302" s="4">
+        <v>99.147999999999996</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>27</v>
-      </c>
-      <c r="B303" s="4">
-        <v>99.137</v>
-      </c>
-      <c r="C303" s="4">
-        <v>99.137</v>
+        <v>28</v>
+      </c>
+      <c r="B303" s="5">
+        <v>99.148099999999999</v>
+      </c>
+      <c r="C303" s="5">
+        <v>99.157899999999998</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>28</v>
-      </c>
-      <c r="B304" s="5">
-        <v>99.137100000000004</v>
-      </c>
-      <c r="C304" s="5">
-        <v>99.147899999999993</v>
+        <v>27</v>
+      </c>
+      <c r="B304" s="4">
+        <v>99.158000000000001</v>
+      </c>
+      <c r="C304" s="4">
+        <v>99.158000000000001</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>27</v>
-      </c>
-      <c r="B305" s="4">
-        <v>99.147999999999996</v>
-      </c>
-      <c r="C305" s="4">
-        <v>99.147999999999996</v>
+        <v>28</v>
+      </c>
+      <c r="B305" s="5">
+        <v>99.158100000000005</v>
+      </c>
+      <c r="C305" s="5">
+        <v>99.167900000000003</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>28</v>
-      </c>
-      <c r="B306" s="5">
-        <v>99.148099999999999</v>
-      </c>
-      <c r="C306" s="5">
-        <v>99.157899999999998</v>
+        <v>27</v>
+      </c>
+      <c r="B306" s="4">
+        <v>99.168000000000006</v>
+      </c>
+      <c r="C306" s="4">
+        <v>99.168000000000006</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>27</v>
-      </c>
-      <c r="B307" s="4">
-        <v>99.158000000000001</v>
-      </c>
-      <c r="C307" s="4">
-        <v>99.158000000000001</v>
+        <v>28</v>
+      </c>
+      <c r="B307" s="5">
+        <v>99.16810000000001</v>
+      </c>
+      <c r="C307" s="5">
+        <v>99.176900000000003</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>28</v>
-      </c>
-      <c r="B308" s="5">
-        <v>99.158100000000005</v>
-      </c>
-      <c r="C308" s="5">
-        <v>99.167900000000003</v>
+        <v>27</v>
+      </c>
+      <c r="B308" s="4">
+        <v>99.177000000000007</v>
+      </c>
+      <c r="C308" s="4">
+        <v>99.177000000000007</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>27</v>
-      </c>
-      <c r="B309" s="4">
-        <v>99.168000000000006</v>
-      </c>
-      <c r="C309" s="4">
-        <v>99.168000000000006</v>
+        <v>28</v>
+      </c>
+      <c r="B309" s="5">
+        <v>99.17710000000001</v>
+      </c>
+      <c r="C309" s="5">
+        <v>99.180899999999994</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>28</v>
-      </c>
-      <c r="B310" s="5">
-        <v>99.16810000000001</v>
-      </c>
-      <c r="C310" s="5">
-        <v>99.176900000000003</v>
+        <v>27</v>
+      </c>
+      <c r="B310" s="4">
+        <v>99.180999999999997</v>
+      </c>
+      <c r="C310" s="4">
+        <v>99.180999999999997</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>27</v>
-      </c>
-      <c r="B311" s="4">
-        <v>99.177000000000007</v>
-      </c>
-      <c r="C311" s="4">
-        <v>99.177000000000007</v>
+        <v>28</v>
+      </c>
+      <c r="B311" s="5">
+        <v>99.181100000000001</v>
+      </c>
+      <c r="C311" s="5">
+        <v>99.186899999999994</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>28</v>
-      </c>
-      <c r="B312" s="5">
-        <v>99.17710000000001</v>
-      </c>
-      <c r="C312" s="5">
-        <v>99.180899999999994</v>
+        <v>27</v>
+      </c>
+      <c r="B312" s="4">
+        <v>99.186999999999998</v>
+      </c>
+      <c r="C312" s="4">
+        <v>99.186999999999998</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>27</v>
-      </c>
-      <c r="B313" s="4">
-        <v>99.180999999999997</v>
-      </c>
-      <c r="C313" s="4">
-        <v>99.180999999999997</v>
+        <v>28</v>
+      </c>
+      <c r="B313" s="5">
+        <v>99.187100000000001</v>
+      </c>
+      <c r="C313" s="5">
+        <v>99.190899999999999</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>28</v>
-      </c>
-      <c r="B314" s="5">
-        <v>99.181100000000001</v>
-      </c>
-      <c r="C314" s="5">
-        <v>99.186899999999994</v>
+        <v>27</v>
+      </c>
+      <c r="B314" s="4">
+        <v>99.191000000000003</v>
+      </c>
+      <c r="C314" s="4">
+        <v>99.191000000000003</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>27</v>
-      </c>
-      <c r="B315" s="4">
-        <v>99.186999999999998</v>
-      </c>
-      <c r="C315" s="4">
-        <v>99.186999999999998</v>
+        <v>28</v>
+      </c>
+      <c r="B315" s="5">
+        <v>99.191100000000006</v>
+      </c>
+      <c r="C315" s="5">
+        <v>99.1999</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>28</v>
-      </c>
-      <c r="B316" s="5">
-        <v>99.187100000000001</v>
-      </c>
-      <c r="C316" s="5">
-        <v>99.190899999999999</v>
+        <v>27</v>
+      </c>
+      <c r="B316" s="4">
+        <v>99.2</v>
+      </c>
+      <c r="C316" s="4">
+        <v>99.2</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>27</v>
-      </c>
-      <c r="B317" s="4">
-        <v>99.191000000000003</v>
-      </c>
-      <c r="C317" s="4">
-        <v>99.191000000000003</v>
+        <v>28</v>
+      </c>
+      <c r="B317" s="5">
+        <v>99.200100000000006</v>
+      </c>
+      <c r="C317" s="5">
+        <v>99.20989999999999</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>28</v>
-      </c>
-      <c r="B318" s="5">
-        <v>99.191100000000006</v>
-      </c>
-      <c r="C318" s="5">
-        <v>99.1999</v>
+        <v>27</v>
+      </c>
+      <c r="B318" s="4">
+        <v>99.21</v>
+      </c>
+      <c r="C318" s="4">
+        <v>99.21</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>27</v>
-      </c>
-      <c r="B319" s="4">
-        <v>99.2</v>
-      </c>
-      <c r="C319" s="4">
-        <v>99.2</v>
+        <v>28</v>
+      </c>
+      <c r="B319" s="5">
+        <v>99.210099999999997</v>
+      </c>
+      <c r="C319" s="5">
+        <v>99.219899999999996</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>28</v>
-      </c>
-      <c r="B320" s="5">
-        <v>99.200100000000006</v>
-      </c>
-      <c r="C320" s="5">
-        <v>99.20989999999999</v>
+        <v>27</v>
+      </c>
+      <c r="B320" s="4">
+        <v>99.22</v>
+      </c>
+      <c r="C320" s="4">
+        <v>99.22</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>27</v>
-      </c>
-      <c r="B321" s="4">
-        <v>99.21</v>
-      </c>
-      <c r="C321" s="4">
-        <v>99.21</v>
+        <v>28</v>
+      </c>
+      <c r="B321" s="5">
+        <v>99.220100000000002</v>
+      </c>
+      <c r="C321" s="5">
+        <v>99.229900000000001</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>28</v>
-      </c>
-      <c r="B322" s="5">
-        <v>99.210099999999997</v>
-      </c>
-      <c r="C322" s="5">
-        <v>99.219899999999996</v>
+        <v>27</v>
+      </c>
+      <c r="B322" s="4">
+        <v>99.23</v>
+      </c>
+      <c r="C322" s="4">
+        <v>99.23</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>27</v>
-      </c>
-      <c r="B323" s="4">
-        <v>99.22</v>
-      </c>
-      <c r="C323" s="4">
-        <v>99.22</v>
+        <v>28</v>
+      </c>
+      <c r="B323" s="5">
+        <v>99.230100000000007</v>
+      </c>
+      <c r="C323" s="5">
+        <v>99.239899999999992</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>28</v>
-      </c>
-      <c r="B324" s="5">
-        <v>99.220100000000002</v>
-      </c>
-      <c r="C324" s="5">
-        <v>99.229900000000001</v>
+        <v>27</v>
+      </c>
+      <c r="B324" s="4">
+        <v>99.24</v>
+      </c>
+      <c r="C324" s="4">
+        <v>99.24</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>27</v>
-      </c>
-      <c r="B325" s="4">
-        <v>99.23</v>
-      </c>
-      <c r="C325" s="4">
-        <v>99.23</v>
+        <v>28</v>
+      </c>
+      <c r="B325" s="5">
+        <v>99.240099999999998</v>
+      </c>
+      <c r="C325" s="5">
+        <v>99.249899999999997</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>28</v>
-      </c>
-      <c r="B326" s="5">
-        <v>99.230100000000007</v>
-      </c>
-      <c r="C326" s="5">
-        <v>99.239899999999992</v>
+        <v>27</v>
+      </c>
+      <c r="B326" s="4">
+        <v>99.25</v>
+      </c>
+      <c r="C326" s="4">
+        <v>99.25</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>27</v>
-      </c>
-      <c r="B327" s="4">
-        <v>99.24</v>
-      </c>
-      <c r="C327" s="4">
-        <v>99.24</v>
+        <v>28</v>
+      </c>
+      <c r="B327" s="5">
+        <v>99.250100000000003</v>
+      </c>
+      <c r="C327" s="5">
+        <v>99.259900000000002</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>28</v>
-      </c>
-      <c r="B328" s="5">
-        <v>99.240099999999998</v>
-      </c>
-      <c r="C328" s="5">
-        <v>99.249899999999997</v>
+        <v>27</v>
+      </c>
+      <c r="B328" s="4">
+        <v>99.26</v>
+      </c>
+      <c r="C328" s="4">
+        <v>99.26</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>27</v>
-      </c>
-      <c r="B329" s="4">
-        <v>99.25</v>
-      </c>
-      <c r="C329" s="4">
-        <v>99.25</v>
+        <v>28</v>
+      </c>
+      <c r="B329" s="5">
+        <v>99.260100000000008</v>
+      </c>
+      <c r="C329" s="5">
+        <v>99.269900000000007</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>28</v>
-      </c>
-      <c r="B330" s="5">
-        <v>99.250100000000003</v>
-      </c>
-      <c r="C330" s="5">
-        <v>99.259900000000002</v>
+        <v>27</v>
+      </c>
+      <c r="B330" s="4">
+        <v>99.27000000000001</v>
+      </c>
+      <c r="C330" s="4">
+        <v>99.27000000000001</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>27</v>
-      </c>
-      <c r="B331" s="4">
-        <v>99.26</v>
-      </c>
-      <c r="C331" s="4">
-        <v>99.26</v>
+        <v>28</v>
+      </c>
+      <c r="B331" s="5">
+        <v>99.270100000000014</v>
+      </c>
+      <c r="C331" s="5">
+        <v>99.279900000000012</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>28</v>
-      </c>
-      <c r="B332" s="5">
-        <v>99.260100000000008</v>
-      </c>
-      <c r="C332" s="5">
-        <v>99.269900000000007</v>
+        <v>27</v>
+      </c>
+      <c r="B332" s="4">
+        <v>99.280000000000015</v>
+      </c>
+      <c r="C332" s="4">
+        <v>99.280000000000015</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>27</v>
-      </c>
-      <c r="B333" s="4">
-        <v>99.27000000000001</v>
-      </c>
-      <c r="C333" s="4">
-        <v>99.27000000000001</v>
+        <v>28</v>
+      </c>
+      <c r="B333" s="5">
+        <v>99.280100000000019</v>
+      </c>
+      <c r="C333" s="5">
+        <v>99.289900000000017</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>28</v>
-      </c>
-      <c r="B334" s="5">
-        <v>99.270100000000014</v>
-      </c>
-      <c r="C334" s="5">
-        <v>99.279900000000012</v>
+        <v>27</v>
+      </c>
+      <c r="B334" s="4">
+        <v>99.29000000000002</v>
+      </c>
+      <c r="C334" s="4">
+        <v>99.29000000000002</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>27</v>
-      </c>
-      <c r="B335" s="4">
-        <v>99.280000000000015</v>
-      </c>
-      <c r="C335" s="4">
-        <v>99.280000000000015</v>
+        <v>28</v>
+      </c>
+      <c r="B335" s="5">
+        <v>99.290100000000024</v>
+      </c>
+      <c r="C335" s="5">
+        <v>99.299900000000022</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>28</v>
-      </c>
-      <c r="B336" s="5">
-        <v>99.280100000000019</v>
-      </c>
-      <c r="C336" s="5">
-        <v>99.289900000000017</v>
+        <v>27</v>
+      </c>
+      <c r="B336" s="4">
+        <v>99.300000000000026</v>
+      </c>
+      <c r="C336" s="4">
+        <v>99.300000000000026</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>27</v>
-      </c>
-      <c r="B337" s="4">
-        <v>99.29000000000002</v>
-      </c>
-      <c r="C337" s="4">
-        <v>99.29000000000002</v>
+        <v>28</v>
+      </c>
+      <c r="B337" s="5">
+        <v>99.300100000000029</v>
+      </c>
+      <c r="C337" s="5">
+        <v>99.309900000000027</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>28</v>
-      </c>
-      <c r="B338" s="5">
-        <v>99.290100000000024</v>
-      </c>
-      <c r="C338" s="5">
-        <v>99.299900000000022</v>
+        <v>27</v>
+      </c>
+      <c r="B338" s="4">
+        <v>99.310000000000031</v>
+      </c>
+      <c r="C338" s="4">
+        <v>99.310000000000031</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>27</v>
-      </c>
-      <c r="B339" s="4">
-        <v>99.300000000000026</v>
-      </c>
-      <c r="C339" s="4">
-        <v>99.300000000000026</v>
+        <v>28</v>
+      </c>
+      <c r="B339" s="5">
+        <v>99.310100000000034</v>
+      </c>
+      <c r="C339" s="5">
+        <v>99.319900000000032</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>28</v>
-      </c>
-      <c r="B340" s="5">
-        <v>99.300100000000029</v>
-      </c>
-      <c r="C340" s="5">
-        <v>99.309900000000027</v>
+        <v>27</v>
+      </c>
+      <c r="B340" s="4">
+        <v>99.320000000000036</v>
+      </c>
+      <c r="C340" s="4">
+        <v>99.320000000000036</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>27</v>
-      </c>
-      <c r="B341" s="4">
-        <v>99.310000000000031</v>
-      </c>
-      <c r="C341" s="4">
-        <v>99.310000000000031</v>
+        <v>28</v>
+      </c>
+      <c r="B341" s="5">
+        <v>99.320100000000039</v>
+      </c>
+      <c r="C341" s="5">
+        <v>99.329900000000038</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>28</v>
-      </c>
-      <c r="B342" s="5">
-        <v>99.310100000000034</v>
-      </c>
-      <c r="C342" s="5">
-        <v>99.319900000000032</v>
+        <v>27</v>
+      </c>
+      <c r="B342" s="4">
+        <v>99.330000000000041</v>
+      </c>
+      <c r="C342" s="4">
+        <v>99.330000000000041</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>27</v>
-      </c>
-      <c r="B343" s="4">
-        <v>99.320000000000036</v>
-      </c>
-      <c r="C343" s="4">
-        <v>99.320000000000036</v>
+        <v>28</v>
+      </c>
+      <c r="B343" s="5">
+        <v>99.330100000000044</v>
+      </c>
+      <c r="C343" s="5">
+        <v>99.339900000000043</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>28</v>
-      </c>
-      <c r="B344" s="5">
-        <v>99.320100000000039</v>
-      </c>
-      <c r="C344" s="5">
-        <v>99.329900000000038</v>
+        <v>27</v>
+      </c>
+      <c r="B344" s="4">
+        <v>99.340000000000046</v>
+      </c>
+      <c r="C344" s="4">
+        <v>99.340000000000046</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>27</v>
-      </c>
-      <c r="B345" s="4">
-        <v>99.330000000000041</v>
-      </c>
-      <c r="C345" s="4">
-        <v>99.330000000000041</v>
+        <v>28</v>
+      </c>
+      <c r="B345" s="5">
+        <v>99.340100000000049</v>
+      </c>
+      <c r="C345" s="5">
+        <v>99.349899999999991</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>28</v>
-      </c>
-      <c r="B346" s="5">
-        <v>99.330100000000044</v>
-      </c>
-      <c r="C346" s="5">
-        <v>99.339900000000043</v>
+        <v>27</v>
+      </c>
+      <c r="B346" s="4">
+        <v>99.35</v>
+      </c>
+      <c r="C346" s="4">
+        <v>99.35</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>27</v>
-      </c>
-      <c r="B347" s="4">
-        <v>99.340000000000046</v>
-      </c>
-      <c r="C347" s="4">
-        <v>99.340000000000046</v>
+        <v>28</v>
+      </c>
+      <c r="B347" s="5">
+        <v>99.350099999999998</v>
+      </c>
+      <c r="C347" s="5">
+        <v>99.359899999999996</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>28</v>
-      </c>
-      <c r="B348" s="5">
-        <v>99.340100000000049</v>
-      </c>
-      <c r="C348" s="5">
-        <v>99.349899999999991</v>
+        <v>27</v>
+      </c>
+      <c r="B348" s="4">
+        <v>99.36</v>
+      </c>
+      <c r="C348" s="4">
+        <v>99.36</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>27</v>
-      </c>
-      <c r="B349" s="4">
-        <v>99.35</v>
-      </c>
-      <c r="C349" s="4">
-        <v>99.35</v>
+        <v>28</v>
+      </c>
+      <c r="B349" s="5">
+        <v>99.360100000000003</v>
+      </c>
+      <c r="C349" s="5">
+        <v>99.369900000000001</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>28</v>
-      </c>
-      <c r="B350" s="5">
-        <v>99.350099999999998</v>
-      </c>
-      <c r="C350" s="5">
-        <v>99.359899999999996</v>
+        <v>27</v>
+      </c>
+      <c r="B350" s="4">
+        <v>99.37</v>
+      </c>
+      <c r="C350" s="4">
+        <v>99.37</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>27</v>
-      </c>
-      <c r="B351" s="4">
-        <v>99.36</v>
-      </c>
-      <c r="C351" s="4">
-        <v>99.36</v>
+        <v>28</v>
+      </c>
+      <c r="B351" s="5">
+        <v>99.370100000000008</v>
+      </c>
+      <c r="C351" s="5">
+        <v>99.379899999999992</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>28</v>
-      </c>
-      <c r="B352" s="5">
-        <v>99.360100000000003</v>
-      </c>
-      <c r="C352" s="5">
-        <v>99.369900000000001</v>
+        <v>27</v>
+      </c>
+      <c r="B352" s="4">
+        <v>99.38</v>
+      </c>
+      <c r="C352" s="4">
+        <v>99.38</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>27</v>
-      </c>
-      <c r="B353" s="4">
-        <v>99.37</v>
-      </c>
-      <c r="C353" s="4">
-        <v>99.37</v>
+        <v>28</v>
+      </c>
+      <c r="B353" s="5">
+        <v>99.380099999999999</v>
+      </c>
+      <c r="C353" s="5">
+        <v>99.389899999999997</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>28</v>
-      </c>
-      <c r="B354" s="5">
-        <v>99.370100000000008</v>
-      </c>
-      <c r="C354" s="5">
-        <v>99.379899999999992</v>
+        <v>27</v>
+      </c>
+      <c r="B354" s="4">
+        <v>99.39</v>
+      </c>
+      <c r="C354" s="4">
+        <v>99.39</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>27</v>
-      </c>
-      <c r="B355" s="4">
-        <v>99.38</v>
-      </c>
-      <c r="C355" s="4">
-        <v>99.38</v>
+        <v>28</v>
+      </c>
+      <c r="B355" s="5">
+        <v>99.390100000000004</v>
+      </c>
+      <c r="C355" s="5">
+        <v>99.400899999999993</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>28</v>
-      </c>
-      <c r="B356" s="5">
-        <v>99.380099999999999</v>
-      </c>
-      <c r="C356" s="5">
-        <v>99.389899999999997</v>
+        <v>27</v>
+      </c>
+      <c r="B356" s="4">
+        <v>99.400999999999996</v>
+      </c>
+      <c r="C356" s="4">
+        <v>99.400999999999996</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>27</v>
-      </c>
-      <c r="B357" s="4">
-        <v>99.39</v>
-      </c>
-      <c r="C357" s="4">
-        <v>99.39</v>
+        <v>28</v>
+      </c>
+      <c r="B357" s="5">
+        <v>99.4011</v>
+      </c>
+      <c r="C357" s="5">
+        <v>99.409899999999993</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>28</v>
-      </c>
-      <c r="B358" s="5">
-        <v>99.390100000000004</v>
-      </c>
-      <c r="C358" s="5">
-        <v>99.400899999999993</v>
+        <v>27</v>
+      </c>
+      <c r="B358" s="4">
+        <v>99.41</v>
+      </c>
+      <c r="C358" s="4">
+        <v>99.41</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>27</v>
-      </c>
-      <c r="B359" s="4">
-        <v>99.400999999999996</v>
-      </c>
-      <c r="C359" s="4">
-        <v>99.400999999999996</v>
+        <v>28</v>
+      </c>
+      <c r="B359" s="5">
+        <v>99.4101</v>
+      </c>
+      <c r="C359" s="5">
+        <v>99.419899999999998</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>28</v>
-      </c>
-      <c r="B360" s="5">
-        <v>99.4011</v>
-      </c>
-      <c r="C360" s="5">
-        <v>99.409899999999993</v>
+        <v>27</v>
+      </c>
+      <c r="B360" s="4">
+        <v>99.42</v>
+      </c>
+      <c r="C360" s="4">
+        <v>99.42</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>27</v>
-      </c>
-      <c r="B361" s="4">
-        <v>99.41</v>
-      </c>
-      <c r="C361" s="4">
-        <v>99.41</v>
+        <v>28</v>
+      </c>
+      <c r="B361" s="5">
+        <v>99.420100000000005</v>
+      </c>
+      <c r="C361" s="5">
+        <v>99.429900000000004</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>28</v>
-      </c>
-      <c r="B362" s="5">
-        <v>99.4101</v>
-      </c>
-      <c r="C362" s="5">
-        <v>99.419899999999998</v>
+        <v>27</v>
+      </c>
+      <c r="B362" s="4">
+        <v>99.43</v>
+      </c>
+      <c r="C362" s="4">
+        <v>99.43</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>27</v>
-      </c>
-      <c r="B363" s="4">
-        <v>99.42</v>
-      </c>
-      <c r="C363" s="4">
-        <v>99.42</v>
+        <v>28</v>
+      </c>
+      <c r="B363" s="5">
+        <v>99.43010000000001</v>
+      </c>
+      <c r="C363" s="5">
+        <v>99.440899999999999</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>28</v>
-      </c>
-      <c r="B364" s="5">
-        <v>99.420100000000005</v>
-      </c>
-      <c r="C364" s="5">
-        <v>99.429900000000004</v>
+        <v>27</v>
+      </c>
+      <c r="B364" s="4">
+        <v>99.441000000000003</v>
+      </c>
+      <c r="C364" s="4">
+        <v>99.441000000000003</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>27</v>
-      </c>
-      <c r="B365" s="4">
-        <v>99.43</v>
-      </c>
-      <c r="C365" s="4">
-        <v>99.43</v>
+        <v>28</v>
+      </c>
+      <c r="B365" s="5">
+        <v>99.441100000000006</v>
+      </c>
+      <c r="C365" s="5">
+        <v>99.4499</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>28</v>
-      </c>
-      <c r="B366" s="5">
-        <v>99.43010000000001</v>
-      </c>
-      <c r="C366" s="5">
-        <v>99.440899999999999</v>
+        <v>27</v>
+      </c>
+      <c r="B366" s="4">
+        <v>99.45</v>
+      </c>
+      <c r="C366" s="4">
+        <v>99.45</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>27</v>
-      </c>
-      <c r="B367" s="4">
-        <v>99.441000000000003</v>
-      </c>
-      <c r="C367" s="4">
-        <v>99.441000000000003</v>
+        <v>28</v>
+      </c>
+      <c r="B367" s="5">
+        <v>99.450100000000006</v>
+      </c>
+      <c r="C367" s="5">
+        <v>99.460899999999995</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>28</v>
-      </c>
-      <c r="B368" s="5">
-        <v>99.441100000000006</v>
-      </c>
-      <c r="C368" s="5">
-        <v>99.4499</v>
+        <v>27</v>
+      </c>
+      <c r="B368" s="4">
+        <v>99.460999999999999</v>
+      </c>
+      <c r="C368" s="4">
+        <v>99.460999999999999</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>27</v>
-      </c>
-      <c r="B369" s="4">
-        <v>99.45</v>
-      </c>
-      <c r="C369" s="4">
-        <v>99.45</v>
+        <v>28</v>
+      </c>
+      <c r="B369" s="5">
+        <v>99.461100000000002</v>
+      </c>
+      <c r="C369" s="5">
+        <v>99.4709</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>28</v>
-      </c>
-      <c r="B370" s="5">
-        <v>99.450100000000006</v>
-      </c>
-      <c r="C370" s="5">
-        <v>99.460899999999995</v>
+        <v>27</v>
+      </c>
+      <c r="B370" s="4">
+        <v>99.471000000000004</v>
+      </c>
+      <c r="C370" s="4">
+        <v>99.471000000000004</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>27</v>
-      </c>
-      <c r="B371" s="4">
-        <v>99.460999999999999</v>
-      </c>
-      <c r="C371" s="4">
-        <v>99.460999999999999</v>
+        <v>28</v>
+      </c>
+      <c r="B371" s="5">
+        <v>99.471100000000007</v>
+      </c>
+      <c r="C371" s="5">
+        <v>99.480899999999991</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>28</v>
-      </c>
-      <c r="B372" s="5">
-        <v>99.461100000000002</v>
-      </c>
-      <c r="C372" s="5">
-        <v>99.4709</v>
+        <v>27</v>
+      </c>
+      <c r="B372" s="4">
+        <v>99.480999999999995</v>
+      </c>
+      <c r="C372" s="4">
+        <v>99.480999999999995</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>27</v>
-      </c>
-      <c r="B373" s="4">
-        <v>99.471000000000004</v>
-      </c>
-      <c r="C373" s="4">
-        <v>99.471000000000004</v>
+        <v>28</v>
+      </c>
+      <c r="B373" s="5">
+        <v>99.481099999999998</v>
+      </c>
+      <c r="C373" s="5">
+        <v>99.491900000000001</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>28</v>
-      </c>
-      <c r="B374" s="5">
-        <v>99.471100000000007</v>
-      </c>
-      <c r="C374" s="5">
-        <v>99.480899999999991</v>
+        <v>27</v>
+      </c>
+      <c r="B374" s="4">
+        <v>99.492000000000004</v>
+      </c>
+      <c r="C374" s="4">
+        <v>99.492000000000004</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>27</v>
-      </c>
-      <c r="B375" s="4">
-        <v>99.480999999999995</v>
-      </c>
-      <c r="C375" s="4">
-        <v>99.480999999999995</v>
+        <v>28</v>
+      </c>
+      <c r="B375" s="5">
+        <v>99.492100000000008</v>
+      </c>
+      <c r="C375" s="5">
+        <v>99.501899999999992</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>28</v>
-      </c>
-      <c r="B376" s="5">
-        <v>99.481099999999998</v>
-      </c>
-      <c r="C376" s="5">
-        <v>99.491900000000001</v>
+        <v>27</v>
+      </c>
+      <c r="B376" s="4">
+        <v>99.501999999999995</v>
+      </c>
+      <c r="C376" s="4">
+        <v>99.501999999999995</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>27</v>
-      </c>
-      <c r="B377" s="4">
-        <v>99.492000000000004</v>
-      </c>
-      <c r="C377" s="4">
-        <v>99.492000000000004</v>
+        <v>28</v>
+      </c>
+      <c r="B377" s="5">
+        <v>99.502099999999999</v>
+      </c>
+      <c r="C377" s="5">
+        <v>99.511899999999997</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>28</v>
-      </c>
-      <c r="B378" s="5">
-        <v>99.492100000000008</v>
-      </c>
-      <c r="C378" s="5">
-        <v>99.501899999999992</v>
+        <v>27</v>
+      </c>
+      <c r="B378" s="4">
+        <v>99.512</v>
+      </c>
+      <c r="C378" s="4">
+        <v>99.512</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>27</v>
-      </c>
-      <c r="B379" s="4">
-        <v>99.501999999999995</v>
-      </c>
-      <c r="C379" s="4">
-        <v>99.501999999999995</v>
+        <v>28</v>
+      </c>
+      <c r="B379" s="5">
+        <v>99.512100000000004</v>
+      </c>
+      <c r="C379" s="5">
+        <v>99.520899999999997</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>28</v>
-      </c>
-      <c r="B380" s="5">
-        <v>99.502099999999999</v>
-      </c>
-      <c r="C380" s="5">
-        <v>99.511899999999997</v>
+        <v>27</v>
+      </c>
+      <c r="B380" s="4">
+        <v>99.521000000000001</v>
+      </c>
+      <c r="C380" s="4">
+        <v>99.521000000000001</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>27</v>
-      </c>
-      <c r="B381" s="4">
-        <v>99.512</v>
-      </c>
-      <c r="C381" s="4">
-        <v>99.512</v>
+        <v>28</v>
+      </c>
+      <c r="B381" s="5">
+        <v>99.521100000000004</v>
+      </c>
+      <c r="C381" s="5">
+        <v>99.528899999999993</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>28</v>
-      </c>
-      <c r="B382" s="5">
-        <v>99.512100000000004</v>
-      </c>
-      <c r="C382" s="5">
-        <v>99.520899999999997</v>
+        <v>27</v>
+      </c>
+      <c r="B382" s="4">
+        <v>99.528999999999996</v>
+      </c>
+      <c r="C382" s="4">
+        <v>99.528999999999996</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>27</v>
-      </c>
-      <c r="B383" s="4">
-        <v>99.521000000000001</v>
-      </c>
-      <c r="C383" s="4">
-        <v>99.521000000000001</v>
+        <v>28</v>
+      </c>
+      <c r="B383" s="5">
+        <v>99.5291</v>
+      </c>
+      <c r="C383" s="5">
+        <v>99.535899999999998</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>28</v>
-      </c>
-      <c r="B384" s="5">
-        <v>99.521100000000004</v>
-      </c>
-      <c r="C384" s="5">
-        <v>99.528899999999993</v>
+        <v>27</v>
+      </c>
+      <c r="B384" s="4">
+        <v>99.534999999999997</v>
+      </c>
+      <c r="C384" s="4">
+        <v>99.534999999999997</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>27</v>
-      </c>
-      <c r="B385" s="4">
-        <v>99.528999999999996</v>
-      </c>
-      <c r="C385" s="4">
-        <v>99.528999999999996</v>
+        <v>28</v>
+      </c>
+      <c r="B385" s="5">
+        <v>99.5351</v>
+      </c>
+      <c r="C385" s="5">
+        <v>99.535899999999998</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>28</v>
-      </c>
-      <c r="B386" s="5">
-        <v>99.5291</v>
-      </c>
-      <c r="C386" s="5">
-        <v>99.535899999999998</v>
+        <v>27</v>
+      </c>
+      <c r="B386" s="4">
+        <v>99.536000000000001</v>
+      </c>
+      <c r="C386" s="4">
+        <v>99.536000000000001</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>27</v>
-      </c>
-      <c r="B387" s="4">
-        <v>99.536000000000001</v>
-      </c>
-      <c r="C387" s="4">
-        <v>99.536000000000001</v>
+        <v>28</v>
+      </c>
+      <c r="B387" s="5">
+        <v>99.536100000000005</v>
+      </c>
+      <c r="C387" s="5">
+        <v>99.536900000000003</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>28</v>
-      </c>
-      <c r="B388" s="5">
-        <v>99.536100000000005</v>
-      </c>
-      <c r="C388" s="5">
-        <v>99.537899999999993</v>
+        <v>27</v>
+      </c>
+      <c r="B388" s="4">
+        <v>99.537000000000006</v>
+      </c>
+      <c r="C388" s="4">
+        <v>99.537000000000006</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>27</v>
-      </c>
-      <c r="B389" s="4">
-        <v>99.537999999999997</v>
-      </c>
-      <c r="C389" s="4">
-        <v>99.537999999999997</v>
+        <v>28</v>
+      </c>
+      <c r="B389" s="5">
+        <v>99.537100000000009</v>
+      </c>
+      <c r="C389" s="5">
+        <v>99.537899999999993</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>28</v>
-      </c>
-      <c r="B390" s="5">
-        <v>99.5381</v>
-      </c>
-      <c r="C390" s="5">
-        <v>99.534899999999993</v>
+        <v>27</v>
+      </c>
+      <c r="B390" s="4">
+        <v>99.537999999999997</v>
+      </c>
+      <c r="C390" s="4">
+        <v>99.537999999999997</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>27</v>
-      </c>
-      <c r="B391" s="4">
-        <v>99.534999999999997</v>
-      </c>
-      <c r="C391" s="4">
-        <v>99.534999999999997</v>
+        <v>28</v>
+      </c>
+      <c r="B391" s="5">
+        <v>99.5381</v>
+      </c>
+      <c r="C391" s="5">
+        <v>99.542900000000003</v>
       </c>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>28</v>
-      </c>
-      <c r="B392" s="5">
-        <v>99.5351</v>
-      </c>
-      <c r="C392" s="5">
-        <v>99.536900000000003</v>
+        <v>27</v>
+      </c>
+      <c r="B392" s="4">
+        <v>99.543000000000006</v>
+      </c>
+      <c r="C392" s="4">
+        <v>99.543000000000006</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>27</v>
-      </c>
-      <c r="B393" s="4">
-        <v>99.537000000000006</v>
-      </c>
-      <c r="C393" s="4">
-        <v>99.537000000000006</v>
+        <v>28</v>
+      </c>
+      <c r="B393" s="5">
+        <v>99.54310000000001</v>
+      </c>
+      <c r="C393" s="5">
+        <v>99.549899999999994</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>28</v>
-      </c>
-      <c r="B394" s="5">
-        <v>99.537100000000009</v>
-      </c>
-      <c r="C394" s="5">
-        <v>99.542900000000003</v>
+        <v>27</v>
+      </c>
+      <c r="B394" s="4">
+        <v>99.55</v>
+      </c>
+      <c r="C394" s="4">
+        <v>99.55</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>27</v>
-      </c>
-      <c r="B395" s="4">
-        <v>99.543000000000006</v>
-      </c>
-      <c r="C395" s="4">
-        <v>99.543000000000006</v>
+        <v>28</v>
+      </c>
+      <c r="B395" s="5">
+        <v>99.5501</v>
+      </c>
+      <c r="C395" s="5">
+        <v>99.559899999999999</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>28</v>
-      </c>
-      <c r="B396" s="5">
-        <v>99.54310000000001</v>
-      </c>
-      <c r="C396" s="5">
-        <v>99.549899999999994</v>
+        <v>27</v>
+      </c>
+      <c r="B396" s="4">
+        <v>99.56</v>
+      </c>
+      <c r="C396" s="4">
+        <v>99.56</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
-        <v>27</v>
-      </c>
-      <c r="B397" s="4">
-        <v>99.55</v>
-      </c>
-      <c r="C397" s="4">
-        <v>99.55</v>
+        <v>28</v>
+      </c>
+      <c r="B397" s="5">
+        <v>99.560100000000006</v>
+      </c>
+      <c r="C397" s="5">
+        <v>99.570899999999995</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
-        <v>28</v>
-      </c>
-      <c r="B398" s="5">
-        <v>99.5501</v>
-      </c>
-      <c r="C398" s="5">
-        <v>99.559899999999999</v>
+        <v>27</v>
+      </c>
+      <c r="B398" s="4">
+        <v>99.570999999999998</v>
+      </c>
+      <c r="C398" s="4">
+        <v>99.570999999999998</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
-        <v>27</v>
-      </c>
-      <c r="B399" s="4">
-        <v>99.56</v>
-      </c>
-      <c r="C399" s="4">
-        <v>99.56</v>
+        <v>28</v>
+      </c>
+      <c r="B399" s="5">
+        <v>99.571100000000001</v>
+      </c>
+      <c r="C399" s="5">
+        <v>99.58189999999999</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>28</v>
-      </c>
-      <c r="B400" s="5">
-        <v>99.560100000000006</v>
-      </c>
-      <c r="C400" s="5">
-        <v>99.570899999999995</v>
+        <v>27</v>
+      </c>
+      <c r="B400" s="4">
+        <v>99.581999999999994</v>
+      </c>
+      <c r="C400" s="4">
+        <v>99.581999999999994</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>27</v>
-      </c>
-      <c r="B401" s="4">
-        <v>99.570999999999998</v>
-      </c>
-      <c r="C401" s="4">
-        <v>99.570999999999998</v>
+        <v>28</v>
+      </c>
+      <c r="B401" s="5">
+        <v>99.582099999999997</v>
+      </c>
+      <c r="C401" s="5">
+        <v>99.5929</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>28</v>
-      </c>
-      <c r="B402" s="5">
-        <v>99.571100000000001</v>
-      </c>
-      <c r="C402" s="5">
-        <v>99.58189999999999</v>
+        <v>27</v>
+      </c>
+      <c r="B402" s="4">
+        <v>99.593000000000004</v>
+      </c>
+      <c r="C402" s="4">
+        <v>99.593000000000004</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>27</v>
-      </c>
-      <c r="B403" s="4">
-        <v>99.581999999999994</v>
-      </c>
-      <c r="C403" s="4">
-        <v>99.581999999999994</v>
+        <v>28</v>
+      </c>
+      <c r="B403" s="5">
+        <v>99.593100000000007</v>
+      </c>
+      <c r="C403" s="5">
+        <v>99.604900000000001</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>28</v>
-      </c>
-      <c r="B404" s="5">
-        <v>99.582099999999997</v>
-      </c>
-      <c r="C404" s="5">
-        <v>99.5929</v>
+        <v>27</v>
+      </c>
+      <c r="B404" s="4">
+        <v>99.605000000000004</v>
+      </c>
+      <c r="C404" s="4">
+        <v>99.605000000000004</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>27</v>
-      </c>
-      <c r="B405" s="4">
-        <v>99.593000000000004</v>
-      </c>
-      <c r="C405" s="4">
-        <v>99.593000000000004</v>
+        <v>28</v>
+      </c>
+      <c r="B405" s="5">
+        <v>99.605100000000007</v>
+      </c>
+      <c r="C405" s="5">
+        <v>99.615899999999996</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>28</v>
-      </c>
-      <c r="B406" s="5">
-        <v>99.593100000000007</v>
-      </c>
-      <c r="C406" s="5">
-        <v>99.604900000000001</v>
+        <v>27</v>
+      </c>
+      <c r="B406" s="4">
+        <v>99.616</v>
+      </c>
+      <c r="C406" s="4">
+        <v>99.616</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>27</v>
-      </c>
-      <c r="B407" s="4">
-        <v>99.605000000000004</v>
-      </c>
-      <c r="C407" s="4">
-        <v>99.605000000000004</v>
+        <v>28</v>
+      </c>
+      <c r="B407" s="5">
+        <v>99.616100000000003</v>
+      </c>
+      <c r="C407" s="5">
+        <v>99.626899999999992</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>28</v>
-      </c>
-      <c r="B408" s="5">
-        <v>99.605100000000007</v>
-      </c>
-      <c r="C408" s="5">
-        <v>99.615899999999996</v>
+        <v>27</v>
+      </c>
+      <c r="B408" s="4">
+        <v>99.626999999999995</v>
+      </c>
+      <c r="C408" s="4">
+        <v>99.626999999999995</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
-        <v>27</v>
-      </c>
-      <c r="B409" s="4">
-        <v>99.616</v>
-      </c>
-      <c r="C409" s="4">
-        <v>99.616</v>
+        <v>28</v>
+      </c>
+      <c r="B409" s="5">
+        <v>99.627099999999999</v>
+      </c>
+      <c r="C409" s="5">
+        <v>99.637900000000002</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
-        <v>28</v>
-      </c>
-      <c r="B410" s="5">
-        <v>99.616100000000003</v>
-      </c>
-      <c r="C410" s="5">
-        <v>99.626899999999992</v>
+        <v>27</v>
+      </c>
+      <c r="B410" s="4">
+        <v>99.638000000000005</v>
+      </c>
+      <c r="C410" s="4">
+        <v>99.638000000000005</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
-        <v>27</v>
-      </c>
-      <c r="B411" s="4">
-        <v>99.626999999999995</v>
-      </c>
-      <c r="C411" s="4">
-        <v>99.626999999999995</v>
+        <v>28</v>
+      </c>
+      <c r="B411" s="5">
+        <v>99.638100000000009</v>
+      </c>
+      <c r="C411" s="5">
+        <v>99.649900000000002</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
-        <v>28</v>
-      </c>
-      <c r="B412" s="5">
-        <v>99.627099999999999</v>
-      </c>
-      <c r="C412" s="5">
-        <v>99.637900000000002</v>
+        <v>27</v>
+      </c>
+      <c r="B412" s="4">
+        <v>99.65</v>
+      </c>
+      <c r="C412" s="4">
+        <v>99.65</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>27</v>
-      </c>
-      <c r="B413" s="4">
-        <v>99.638000000000005</v>
-      </c>
-      <c r="C413" s="4">
-        <v>99.638000000000005</v>
+        <v>28</v>
+      </c>
+      <c r="B413" s="5">
+        <v>99.650100000000009</v>
+      </c>
+      <c r="C413" s="5">
+        <v>99.660899999999998</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
-        <v>28</v>
-      </c>
-      <c r="B414" s="5">
-        <v>99.638100000000009</v>
-      </c>
-      <c r="C414" s="5">
-        <v>99.649900000000002</v>
+        <v>27</v>
+      </c>
+      <c r="B414" s="4">
+        <v>99.661000000000001</v>
+      </c>
+      <c r="C414" s="4">
+        <v>99.661000000000001</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>27</v>
-      </c>
-      <c r="B415" s="4">
-        <v>99.65</v>
-      </c>
-      <c r="C415" s="4">
-        <v>99.65</v>
+        <v>28</v>
+      </c>
+      <c r="B415" s="5">
+        <v>99.661100000000005</v>
+      </c>
+      <c r="C415" s="5">
+        <v>99.672899999999998</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>28</v>
-      </c>
-      <c r="B416" s="5">
-        <v>99.650100000000009</v>
-      </c>
-      <c r="C416" s="5">
-        <v>99.660899999999998</v>
+        <v>27</v>
+      </c>
+      <c r="B416" s="4">
+        <v>99.673000000000002</v>
+      </c>
+      <c r="C416" s="4">
+        <v>99.673000000000002</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>27</v>
-      </c>
-      <c r="B417" s="4">
-        <v>99.661000000000001</v>
-      </c>
-      <c r="C417" s="4">
-        <v>99.661000000000001</v>
+        <v>28</v>
+      </c>
+      <c r="B417" s="5">
+        <v>99.673100000000005</v>
+      </c>
+      <c r="C417" s="5">
+        <v>99.683899999999994</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>28</v>
-      </c>
-      <c r="B418" s="5">
-        <v>99.661100000000005</v>
-      </c>
-      <c r="C418" s="5">
-        <v>99.672899999999998</v>
+        <v>27</v>
+      </c>
+      <c r="B418" s="4">
+        <v>99.683999999999997</v>
+      </c>
+      <c r="C418" s="4">
+        <v>99.683999999999997</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
-        <v>27</v>
-      </c>
-      <c r="B419" s="4">
-        <v>99.673000000000002</v>
-      </c>
-      <c r="C419" s="4">
-        <v>99.673000000000002</v>
+        <v>28</v>
+      </c>
+      <c r="B419" s="5">
+        <v>99.684100000000001</v>
+      </c>
+      <c r="C419" s="5">
+        <v>99.695899999999995</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
-        <v>28</v>
-      </c>
-      <c r="B420" s="5">
-        <v>99.673100000000005</v>
-      </c>
-      <c r="C420" s="5">
-        <v>99.683899999999994</v>
+        <v>27</v>
+      </c>
+      <c r="B420" s="4">
+        <v>99.695999999999998</v>
+      </c>
+      <c r="C420" s="4">
+        <v>99.695999999999998</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
-        <v>27</v>
-      </c>
-      <c r="B421" s="4">
-        <v>99.683999999999997</v>
-      </c>
-      <c r="C421" s="4">
-        <v>99.683999999999997</v>
+        <v>28</v>
+      </c>
+      <c r="B421" s="5">
+        <v>99.696100000000001</v>
+      </c>
+      <c r="C421" s="5">
+        <v>99.7059</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
-        <v>28</v>
-      </c>
-      <c r="B422" s="5">
-        <v>99.684100000000001</v>
-      </c>
-      <c r="C422" s="5">
-        <v>99.695899999999995</v>
+        <v>27</v>
+      </c>
+      <c r="B422" s="4">
+        <v>99.706000000000003</v>
+      </c>
+      <c r="C422" s="4">
+        <v>99.706000000000003</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>27</v>
-      </c>
-      <c r="B423" s="4">
-        <v>99.695999999999998</v>
-      </c>
-      <c r="C423" s="4">
-        <v>99.695999999999998</v>
+        <v>28</v>
+      </c>
+      <c r="B423" s="5">
+        <v>99.706100000000006</v>
+      </c>
+      <c r="C423" s="5">
+        <v>99.7179</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>28</v>
-      </c>
-      <c r="B424" s="5">
-        <v>99.696100000000001</v>
-      </c>
-      <c r="C424" s="5">
-        <v>99.7059</v>
+        <v>27</v>
+      </c>
+      <c r="B424" s="4">
+        <v>99.718000000000004</v>
+      </c>
+      <c r="C424" s="4">
+        <v>99.718000000000004</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>27</v>
-      </c>
-      <c r="B425" s="4">
-        <v>99.706000000000003</v>
-      </c>
-      <c r="C425" s="4">
-        <v>99.706000000000003</v>
+        <v>28</v>
+      </c>
+      <c r="B425" s="5">
+        <v>99.718100000000007</v>
+      </c>
+      <c r="C425" s="5">
+        <v>99.727899999999991</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>28</v>
-      </c>
-      <c r="B426" s="5">
-        <v>99.706100000000006</v>
-      </c>
-      <c r="C426" s="5">
-        <v>99.7179</v>
+        <v>27</v>
+      </c>
+      <c r="B426" s="4">
+        <v>99.727999999999994</v>
+      </c>
+      <c r="C426" s="4">
+        <v>99.727999999999994</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>27</v>
-      </c>
-      <c r="B427" s="4">
-        <v>99.718000000000004</v>
-      </c>
-      <c r="C427" s="4">
-        <v>99.718000000000004</v>
+        <v>28</v>
+      </c>
+      <c r="B427" s="5">
+        <v>99.728099999999998</v>
+      </c>
+      <c r="C427" s="5">
+        <v>99.735900000000001</v>
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>28</v>
-      </c>
-      <c r="B428" s="5">
-        <v>99.718100000000007</v>
-      </c>
-      <c r="C428" s="5">
-        <v>99.727899999999991</v>
+        <v>27</v>
+      </c>
+      <c r="B428" s="4">
+        <v>99.736000000000004</v>
+      </c>
+      <c r="C428" s="4">
+        <v>99.736000000000004</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
-        <v>27</v>
-      </c>
-      <c r="B429" s="4">
-        <v>99.727999999999994</v>
-      </c>
-      <c r="C429" s="4">
-        <v>99.727999999999994</v>
+        <v>28</v>
+      </c>
+      <c r="B429" s="5">
+        <v>99.736100000000008</v>
+      </c>
+      <c r="C429" s="5">
+        <v>99.741900000000001</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>28</v>
-      </c>
-      <c r="B430" s="5">
-        <v>99.728099999999998</v>
-      </c>
-      <c r="C430" s="5">
-        <v>99.735900000000001</v>
+        <v>27</v>
+      </c>
+      <c r="B430" s="4">
+        <v>99.742000000000004</v>
+      </c>
+      <c r="C430" s="4">
+        <v>99.742000000000004</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>27</v>
-      </c>
-      <c r="B431" s="4">
-        <v>99.736000000000004</v>
-      </c>
-      <c r="C431" s="4">
-        <v>99.736000000000004</v>
+        <v>28</v>
+      </c>
+      <c r="B431" s="5">
+        <v>99.742100000000008</v>
+      </c>
+      <c r="C431" s="5">
+        <v>99.745899999999992</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>28</v>
-      </c>
-      <c r="B432" s="5">
-        <v>99.736100000000008</v>
-      </c>
-      <c r="C432" s="5">
-        <v>99.741900000000001</v>
+        <v>27</v>
+      </c>
+      <c r="B432" s="4">
+        <v>99.745999999999995</v>
+      </c>
+      <c r="C432" s="4">
+        <v>99.745999999999995</v>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>27</v>
-      </c>
-      <c r="B433" s="4">
-        <v>99.742000000000004</v>
-      </c>
-      <c r="C433" s="4">
-        <v>99.742000000000004</v>
+        <v>28</v>
+      </c>
+      <c r="B433" s="5">
+        <v>99.746099999999998</v>
+      </c>
+      <c r="C433" s="5">
+        <v>99.752899999999997</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>28</v>
-      </c>
-      <c r="B434" s="5">
-        <v>99.742100000000008</v>
-      </c>
-      <c r="C434" s="5">
-        <v>99.745899999999992</v>
+        <v>27</v>
+      </c>
+      <c r="B434" s="4">
+        <v>99.753</v>
+      </c>
+      <c r="C434" s="4">
+        <v>99.753</v>
       </c>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>27</v>
-      </c>
-      <c r="B435" s="4">
-        <v>99.745999999999995</v>
-      </c>
-      <c r="C435" s="4">
-        <v>99.745999999999995</v>
+        <v>28</v>
+      </c>
+      <c r="B435" s="5">
+        <v>99.753100000000003</v>
+      </c>
+      <c r="C435" s="5">
+        <v>99.759900000000002</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>28</v>
-      </c>
-      <c r="B436" s="5">
-        <v>99.746099999999998</v>
-      </c>
-      <c r="C436" s="5">
-        <v>99.752899999999997</v>
+        <v>27</v>
+      </c>
+      <c r="B436" s="4">
+        <v>99.76</v>
+      </c>
+      <c r="C436" s="4">
+        <v>99.76</v>
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>27</v>
-      </c>
-      <c r="B437" s="4">
-        <v>99.753</v>
-      </c>
-      <c r="C437" s="4">
-        <v>99.753</v>
+        <v>28</v>
+      </c>
+      <c r="B437" s="5">
+        <v>99.760100000000008</v>
+      </c>
+      <c r="C437" s="5">
+        <v>99.768900000000002</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
-        <v>28</v>
-      </c>
-      <c r="B438" s="5">
-        <v>99.753100000000003</v>
-      </c>
-      <c r="C438" s="5">
-        <v>99.759900000000002</v>
+        <v>27</v>
+      </c>
+      <c r="B438" s="4">
+        <v>99.769000000000005</v>
+      </c>
+      <c r="C438" s="4">
+        <v>99.769000000000005</v>
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
-        <v>27</v>
-      </c>
-      <c r="B439" s="4">
-        <v>99.76</v>
-      </c>
-      <c r="C439" s="4">
-        <v>99.76</v>
+        <v>28</v>
+      </c>
+      <c r="B439" s="5">
+        <v>99.769100000000009</v>
+      </c>
+      <c r="C439" s="5">
+        <v>99.776899999999998</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
-        <v>28</v>
-      </c>
-      <c r="B440" s="5">
-        <v>99.760100000000008</v>
-      </c>
-      <c r="C440" s="5">
-        <v>99.768900000000002</v>
+        <v>27</v>
+      </c>
+      <c r="B440" s="4">
+        <v>99.777000000000001</v>
+      </c>
+      <c r="C440" s="4">
+        <v>99.777000000000001</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
-        <v>27</v>
-      </c>
-      <c r="B441" s="4">
-        <v>99.769000000000005</v>
-      </c>
-      <c r="C441" s="4">
-        <v>99.769000000000005</v>
+        <v>28</v>
+      </c>
+      <c r="B441" s="5">
+        <v>99.777100000000004</v>
+      </c>
+      <c r="C441" s="5">
+        <v>99.788899999999998</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>28</v>
-      </c>
-      <c r="B442" s="5">
-        <v>99.769100000000009</v>
-      </c>
-      <c r="C442" s="5">
-        <v>99.776899999999998</v>
+        <v>27</v>
+      </c>
+      <c r="B442" s="4">
+        <v>99.789000000000001</v>
+      </c>
+      <c r="C442" s="4">
+        <v>99.789000000000001</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>27</v>
-      </c>
-      <c r="B443" s="4">
-        <v>99.777000000000001</v>
-      </c>
-      <c r="C443" s="4">
-        <v>99.777000000000001</v>
+        <v>28</v>
+      </c>
+      <c r="B443" s="5">
+        <v>99.789100000000005</v>
+      </c>
+      <c r="C443" s="5">
+        <v>99.793899999999994</v>
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
-        <v>28</v>
-      </c>
-      <c r="B444" s="5">
-        <v>99.777100000000004</v>
-      </c>
-      <c r="C444" s="5">
-        <v>99.788899999999998</v>
+        <v>27</v>
+      </c>
+      <c r="B444" s="4">
+        <v>99.793999999999997</v>
+      </c>
+      <c r="C444" s="4">
+        <v>99.793999999999997</v>
       </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>27</v>
-      </c>
-      <c r="B445" s="4">
-        <v>99.789000000000001</v>
-      </c>
-      <c r="C445" s="4">
-        <v>99.789000000000001</v>
+        <v>28</v>
+      </c>
+      <c r="B445" s="5">
+        <v>99.7941</v>
+      </c>
+      <c r="C445" s="5">
+        <v>99.804900000000004</v>
       </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
-        <v>28</v>
-      </c>
-      <c r="B446" s="5">
-        <v>99.789100000000005</v>
-      </c>
-      <c r="C446" s="5">
-        <v>99.793899999999994</v>
+        <v>27</v>
+      </c>
+      <c r="B446" s="4">
+        <v>99.805000000000007</v>
+      </c>
+      <c r="C446" s="4">
+        <v>99.805000000000007</v>
       </c>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
-        <v>27</v>
-      </c>
-      <c r="B447" s="4">
-        <v>99.793999999999997</v>
-      </c>
-      <c r="C447" s="4">
-        <v>99.793999999999997</v>
+        <v>28</v>
+      </c>
+      <c r="B447" s="5">
+        <v>99.80510000000001</v>
+      </c>
+      <c r="C447" s="5">
+        <v>99.81389999999999</v>
       </c>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
-        <v>28</v>
-      </c>
-      <c r="B448" s="5">
-        <v>99.7941</v>
-      </c>
-      <c r="C448" s="5">
-        <v>99.804900000000004</v>
+        <v>27</v>
+      </c>
+      <c r="B448" s="4">
+        <v>99.813999999999993</v>
+      </c>
+      <c r="C448" s="4">
+        <v>99.813999999999993</v>
       </c>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
-        <v>27</v>
-      </c>
-      <c r="B449" s="4">
-        <v>99.805000000000007</v>
-      </c>
-      <c r="C449" s="4">
-        <v>99.805000000000007</v>
+        <v>28</v>
+      </c>
+      <c r="B449" s="5">
+        <v>99.814099999999996</v>
+      </c>
+      <c r="C449" s="5">
+        <v>99.82289999999999</v>
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
-        <v>28</v>
-      </c>
-      <c r="B450" s="5">
-        <v>99.80510000000001</v>
-      </c>
-      <c r="C450" s="5">
-        <v>99.81389999999999</v>
+        <v>27</v>
+      </c>
+      <c r="B450" s="4">
+        <v>99.822999999999993</v>
+      </c>
+      <c r="C450" s="4">
+        <v>99.822999999999993</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
-        <v>27</v>
-      </c>
-      <c r="B451" s="4">
-        <v>99.813999999999993</v>
-      </c>
-      <c r="C451" s="4">
-        <v>99.813999999999993</v>
+        <v>28</v>
+      </c>
+      <c r="B451" s="5">
+        <v>99.823099999999997</v>
+      </c>
+      <c r="C451" s="5">
+        <v>99.83189999999999</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
-        <v>28</v>
-      </c>
-      <c r="B452" s="5">
-        <v>99.814099999999996</v>
-      </c>
-      <c r="C452" s="5">
-        <v>99.82289999999999</v>
+        <v>27</v>
+      </c>
+      <c r="B452" s="4">
+        <v>99.831999999999994</v>
+      </c>
+      <c r="C452" s="4">
+        <v>99.831999999999994</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>27</v>
-      </c>
-      <c r="B453" s="4">
-        <v>99.822999999999993</v>
-      </c>
-      <c r="C453" s="4">
-        <v>99.822999999999993</v>
+        <v>28</v>
+      </c>
+      <c r="B453" s="5">
+        <v>99.832099999999997</v>
+      </c>
+      <c r="C453" s="5">
+        <v>99.840899999999991</v>
       </c>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
-        <v>28</v>
-      </c>
-      <c r="B454" s="5">
-        <v>99.823099999999997</v>
-      </c>
-      <c r="C454" s="5">
-        <v>99.83189999999999</v>
+        <v>27</v>
+      </c>
+      <c r="B454" s="4">
+        <v>99.840999999999994</v>
+      </c>
+      <c r="C454" s="4">
+        <v>99.840999999999994</v>
       </c>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
-        <v>27</v>
-      </c>
-      <c r="B455" s="4">
-        <v>99.831999999999994</v>
-      </c>
-      <c r="C455" s="4">
-        <v>99.831999999999994</v>
+        <v>28</v>
+      </c>
+      <c r="B455" s="5">
+        <v>99.841099999999997</v>
+      </c>
+      <c r="C455" s="5">
+        <v>99.849899999999991</v>
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
-        <v>28</v>
-      </c>
-      <c r="B456" s="5">
-        <v>99.832099999999997</v>
-      </c>
-      <c r="C456" s="5">
-        <v>99.840899999999991</v>
+        <v>27</v>
+      </c>
+      <c r="B456" s="4">
+        <v>99.85</v>
+      </c>
+      <c r="C456" s="4">
+        <v>99.85</v>
       </c>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
-        <v>27</v>
-      </c>
-      <c r="B457" s="4">
-        <v>99.840999999999994</v>
-      </c>
-      <c r="C457" s="4">
-        <v>99.840999999999994</v>
+        <v>28</v>
+      </c>
+      <c r="B457" s="5">
+        <v>99.850099999999998</v>
+      </c>
+      <c r="C457" s="5">
+        <v>99.859899999999996</v>
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
-        <v>28</v>
-      </c>
-      <c r="B458" s="5">
-        <v>99.841099999999997</v>
-      </c>
-      <c r="C458" s="5">
-        <v>99.849899999999991</v>
+        <v>27</v>
+      </c>
+      <c r="B458" s="4">
+        <v>99.86</v>
+      </c>
+      <c r="C458" s="4">
+        <v>99.86</v>
       </c>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>27</v>
-      </c>
-      <c r="B459" s="4">
-        <v>99.85</v>
-      </c>
-      <c r="C459" s="4">
-        <v>99.85</v>
+        <v>28</v>
+      </c>
+      <c r="B459" s="5">
+        <v>99.860100000000003</v>
+      </c>
+      <c r="C459" s="5">
+        <v>99.868899999999996</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
-        <v>28</v>
-      </c>
-      <c r="B460" s="5">
-        <v>99.850099999999998</v>
-      </c>
-      <c r="C460" s="5">
-        <v>99.859899999999996</v>
+        <v>27</v>
+      </c>
+      <c r="B460" s="4">
+        <v>99.869</v>
+      </c>
+      <c r="C460" s="4">
+        <v>99.869</v>
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
-        <v>27</v>
-      </c>
-      <c r="B461" s="4">
-        <v>99.86</v>
-      </c>
-      <c r="C461" s="4">
-        <v>99.86</v>
+        <v>28</v>
+      </c>
+      <c r="B461" s="5">
+        <v>99.869100000000003</v>
+      </c>
+      <c r="C461" s="5">
+        <v>99.876899999999992</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
-        <v>28</v>
-      </c>
-      <c r="B462" s="5">
-        <v>99.860100000000003</v>
-      </c>
-      <c r="C462" s="5">
-        <v>99.868899999999996</v>
+        <v>27</v>
+      </c>
+      <c r="B462" s="4">
+        <v>99.876999999999995</v>
+      </c>
+      <c r="C462" s="4">
+        <v>99.876999999999995</v>
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
-        <v>27</v>
-      </c>
-      <c r="B463" s="4">
-        <v>99.869</v>
-      </c>
-      <c r="C463" s="4">
-        <v>99.869</v>
+        <v>28</v>
+      </c>
+      <c r="B463" s="5">
+        <v>99.877099999999999</v>
+      </c>
+      <c r="C463" s="5">
+        <v>99.885899999999992</v>
       </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
-        <v>28</v>
-      </c>
-      <c r="B464" s="5">
-        <v>99.869100000000003</v>
-      </c>
-      <c r="C464" s="5">
-        <v>99.876899999999992</v>
+        <v>27</v>
+      </c>
+      <c r="B464" s="4">
+        <v>99.885999999999996</v>
+      </c>
+      <c r="C464" s="4">
+        <v>99.885999999999996</v>
       </c>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
-        <v>27</v>
-      </c>
-      <c r="B465" s="4">
-        <v>99.876999999999995</v>
-      </c>
-      <c r="C465" s="4">
-        <v>99.876999999999995</v>
+        <v>28</v>
+      </c>
+      <c r="B465" s="5">
+        <v>99.886099999999999</v>
+      </c>
+      <c r="C465" s="5">
+        <v>99.896900000000002</v>
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
-        <v>28</v>
-      </c>
-      <c r="B466" s="5">
-        <v>99.877099999999999</v>
-      </c>
-      <c r="C466" s="5">
-        <v>99.885899999999992</v>
+        <v>27</v>
+      </c>
+      <c r="B466" s="4">
+        <v>99.897000000000006</v>
+      </c>
+      <c r="C466" s="4">
+        <v>99.897000000000006</v>
       </c>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
-        <v>27</v>
-      </c>
-      <c r="B467" s="4">
-        <v>99.885999999999996</v>
-      </c>
-      <c r="C467" s="4">
-        <v>99.885999999999996</v>
+        <v>28</v>
+      </c>
+      <c r="B467" s="5">
+        <v>99.897100000000009</v>
+      </c>
+      <c r="C467" s="5">
+        <v>99.905900000000003</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
-        <v>28</v>
-      </c>
-      <c r="B468" s="5">
-        <v>99.886099999999999</v>
-      </c>
-      <c r="C468" s="5">
-        <v>99.896900000000002</v>
+        <v>27</v>
+      </c>
+      <c r="B468" s="4">
+        <v>99.906000000000006</v>
+      </c>
+      <c r="C468" s="4">
+        <v>99.906000000000006</v>
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
-        <v>27</v>
-      </c>
-      <c r="B469" s="4">
-        <v>99.897000000000006</v>
-      </c>
-      <c r="C469" s="4">
-        <v>99.897000000000006</v>
+        <v>28</v>
+      </c>
+      <c r="B469" s="5">
+        <v>99.906100000000009</v>
+      </c>
+      <c r="C469" s="5">
+        <v>99.912899999999993</v>
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
-        <v>28</v>
-      </c>
-      <c r="B470" s="5">
-        <v>99.897100000000009</v>
-      </c>
-      <c r="C470" s="5">
-        <v>99.905900000000003</v>
+        <v>27</v>
+      </c>
+      <c r="B470" s="4">
+        <v>99.912999999999997</v>
+      </c>
+      <c r="C470" s="4">
+        <v>99.912999999999997</v>
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
-        <v>27</v>
-      </c>
-      <c r="B471" s="4">
-        <v>99.906000000000006</v>
-      </c>
-      <c r="C471" s="4">
-        <v>99.906000000000006</v>
+        <v>28</v>
+      </c>
+      <c r="B471" s="5">
+        <v>99.9131</v>
+      </c>
+      <c r="C471" s="5">
+        <v>99.921899999999994</v>
       </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
-        <v>28</v>
-      </c>
-      <c r="B472" s="5">
-        <v>99.906100000000009</v>
-      </c>
-      <c r="C472" s="5">
-        <v>99.912899999999993</v>
+        <v>27</v>
+      </c>
+      <c r="B472" s="4">
+        <v>99.921999999999997</v>
+      </c>
+      <c r="C472" s="4">
+        <v>99.921999999999997</v>
       </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
-        <v>27</v>
-      </c>
-      <c r="B473" s="4">
-        <v>99.912999999999997</v>
-      </c>
-      <c r="C473" s="4">
-        <v>99.912999999999997</v>
+        <v>28</v>
+      </c>
+      <c r="B473" s="5">
+        <v>99.9221</v>
+      </c>
+      <c r="C473" s="5">
+        <v>99.927899999999994</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
-        <v>28</v>
-      </c>
-      <c r="B474" s="5">
-        <v>99.9131</v>
-      </c>
-      <c r="C474" s="5">
-        <v>99.921899999999994</v>
+        <v>27</v>
+      </c>
+      <c r="B474" s="4">
+        <v>99.927999999999997</v>
+      </c>
+      <c r="C474" s="4">
+        <v>99.927999999999997</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
-        <v>27</v>
-      </c>
-      <c r="B475" s="4">
-        <v>99.921999999999997</v>
-      </c>
-      <c r="C475" s="4">
-        <v>99.921999999999997</v>
+        <v>28</v>
+      </c>
+      <c r="B475" s="5">
+        <v>99.928100000000001</v>
+      </c>
+      <c r="C475" s="5">
+        <v>99.931899999999999</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
-        <v>28</v>
-      </c>
-      <c r="B476" s="5">
-        <v>99.9221</v>
-      </c>
-      <c r="C476" s="5">
-        <v>99.927899999999994</v>
+        <v>27</v>
+      </c>
+      <c r="B476" s="4">
+        <v>99.932000000000002</v>
+      </c>
+      <c r="C476" s="4">
+        <v>99.932000000000002</v>
       </c>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
-        <v>27</v>
-      </c>
-      <c r="B477" s="4">
-        <v>99.927999999999997</v>
-      </c>
-      <c r="C477" s="4">
-        <v>99.927999999999997</v>
+        <v>28</v>
+      </c>
+      <c r="B477" s="5">
+        <v>99.932100000000005</v>
+      </c>
+      <c r="C477" s="5">
+        <v>99.933899999999994</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
-        <v>28</v>
-      </c>
-      <c r="B478" s="5">
-        <v>99.928100000000001</v>
-      </c>
-      <c r="C478" s="5">
-        <v>99.83189999999999</v>
+        <v>27</v>
+      </c>
+      <c r="B478" s="4">
+        <v>99.933999999999997</v>
+      </c>
+      <c r="C478" s="4">
+        <v>99.933999999999997</v>
       </c>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
-        <v>27</v>
-      </c>
-      <c r="B479" s="4">
-        <v>99.831999999999994</v>
-      </c>
-      <c r="C479" s="4">
-        <v>99.831999999999994</v>
+        <v>28</v>
+      </c>
+      <c r="B479" s="5">
+        <v>99.934100000000001</v>
+      </c>
+      <c r="C479" s="5">
+        <v>99.9589</v>
       </c>
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B480" s="5">
-        <v>99.832099999999997</v>
+        <v>99.959000000000003</v>
       </c>
       <c r="C480" s="5">
-        <v>99.933899999999994</v>
+        <v>99.959000000000003</v>
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
-        <v>27</v>
-      </c>
-      <c r="B481" s="4">
-        <v>99.933999999999997</v>
-      </c>
-      <c r="C481" s="4">
-        <v>99.933999999999997</v>
+        <v>28</v>
+      </c>
+      <c r="B481" s="5">
+        <v>99.959100000000007</v>
+      </c>
+      <c r="C481" s="5">
+        <v>100.2239</v>
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B482" s="5">
-        <v>99.934100000000001</v>
+        <v>99.98</v>
       </c>
       <c r="C482" s="5">
-        <v>99.9589</v>
+        <v>99.98</v>
       </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A483" s="13" t="s">
-        <v>27</v>
+      <c r="A483" t="s">
+        <v>28</v>
       </c>
       <c r="B483" s="5">
-        <v>99.959000000000003</v>
+        <v>99.980100000000007</v>
       </c>
       <c r="C483" s="5">
-        <v>99.959000000000003</v>
+        <v>100.0069</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A484" s="13" t="s">
-        <v>28</v>
+      <c r="A484" t="s">
+        <v>27</v>
       </c>
       <c r="B484" s="5">
-        <v>99.959100000000007</v>
+        <v>100.00700000000001</v>
       </c>
       <c r="C484" s="5">
-        <v>100.2239</v>
-      </c>
-    </row>
-    <row r="485" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A485" s="13" t="s">
-        <v>27</v>
+        <v>100.00700000000001</v>
+      </c>
+    </row>
+    <row r="485" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A485" t="s">
+        <v>28</v>
       </c>
       <c r="B485" s="5">
-        <v>99.98</v>
+        <v>100.00710000000001</v>
       </c>
       <c r="C485" s="5">
-        <v>99.98</v>
-      </c>
-    </row>
-    <row r="486" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A486" s="13" t="s">
-        <v>28</v>
+        <v>100.0309</v>
+      </c>
+    </row>
+    <row r="486" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A486" t="s">
+        <v>27</v>
       </c>
       <c r="B486" s="5">
-        <v>99.980100000000007</v>
+        <v>100.03100000000001</v>
       </c>
       <c r="C486" s="5">
-        <v>100.0069</v>
-      </c>
-    </row>
-    <row r="487" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A487" s="13" t="s">
-        <v>27</v>
+        <v>100.03100000000001</v>
+      </c>
+    </row>
+    <row r="487" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A487" t="s">
+        <v>28</v>
       </c>
       <c r="B487" s="5">
-        <v>100.00700000000001</v>
+        <v>100.03110000000001</v>
       </c>
       <c r="C487" s="5">
-        <v>100.00700000000001</v>
-      </c>
-    </row>
-    <row r="488" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A488" s="13" t="s">
-        <v>28</v>
+        <v>100.0569</v>
+      </c>
+    </row>
+    <row r="488" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A488" t="s">
+        <v>27</v>
       </c>
       <c r="B488" s="5">
-        <v>100.00710000000001</v>
+        <v>100.057</v>
       </c>
       <c r="C488" s="5">
-        <v>100.0309</v>
-      </c>
-    </row>
-    <row r="489" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A489" s="13" t="s">
-        <v>27</v>
+        <v>100.057</v>
+      </c>
+    </row>
+    <row r="489" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A489" t="s">
+        <v>28</v>
       </c>
       <c r="B489" s="5">
-        <v>100.03100000000001</v>
+        <v>100.05710000000001</v>
       </c>
       <c r="C489" s="5">
-        <v>100.03100000000001</v>
-      </c>
-    </row>
-    <row r="490" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A490" s="13" t="s">
-        <v>28</v>
+        <v>100.1049</v>
+      </c>
+    </row>
+    <row r="490" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A490" t="s">
+        <v>27</v>
       </c>
       <c r="B490" s="5">
-        <v>100.03110000000001</v>
+        <v>100.105</v>
       </c>
       <c r="C490" s="5">
-        <v>100.0569</v>
-      </c>
-    </row>
-    <row r="491" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A491" s="13" t="s">
-        <v>27</v>
+        <v>100.105</v>
+      </c>
+    </row>
+    <row r="491" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A491" t="s">
+        <v>28</v>
       </c>
       <c r="B491" s="5">
-        <v>100.057</v>
+        <v>100.10510000000001</v>
       </c>
       <c r="C491" s="5">
-        <v>100.057</v>
-      </c>
-    </row>
-    <row r="492" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A492" s="13" t="s">
-        <v>28</v>
+        <v>100.1579</v>
+      </c>
+    </row>
+    <row r="492" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A492" t="s">
+        <v>27</v>
       </c>
       <c r="B492" s="5">
-        <v>100.05710000000001</v>
+        <v>100.158</v>
       </c>
       <c r="C492" s="5">
-        <v>100.1049</v>
-      </c>
-    </row>
-    <row r="493" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A493" s="13" t="s">
-        <v>27</v>
+        <v>100.158</v>
+      </c>
+    </row>
+    <row r="493" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A493" t="s">
+        <v>28</v>
       </c>
       <c r="B493" s="5">
-        <v>100.105</v>
+        <v>100.1581</v>
       </c>
       <c r="C493" s="5">
-        <v>100.105</v>
-      </c>
-    </row>
-    <row r="494" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A494" s="13" t="s">
-        <v>28</v>
+        <v>100.2079</v>
+      </c>
+    </row>
+    <row r="494" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A494" t="s">
+        <v>27</v>
       </c>
       <c r="B494" s="5">
-        <v>100.10510000000001</v>
+        <v>100.208</v>
       </c>
       <c r="C494" s="5">
-        <v>100.1579</v>
-      </c>
-    </row>
-    <row r="495" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A495" s="13" t="s">
-        <v>27</v>
+        <v>100.208</v>
+      </c>
+    </row>
+    <row r="495" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A495" t="s">
+        <v>28</v>
       </c>
       <c r="B495" s="5">
-        <v>100.158</v>
+        <v>100.2081</v>
       </c>
       <c r="C495" s="5">
-        <v>100.158</v>
-      </c>
-    </row>
-    <row r="496" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A496" s="13" t="s">
-        <v>28</v>
+        <v>100.2409</v>
+      </c>
+    </row>
+    <row r="496" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A496" t="s">
+        <v>27</v>
       </c>
       <c r="B496" s="5">
-        <v>100.1581</v>
+        <v>100.241</v>
       </c>
       <c r="C496" s="5">
-        <v>100.2079</v>
-      </c>
-    </row>
-    <row r="497" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A497" s="13" t="s">
-        <v>27</v>
+        <v>100.241</v>
+      </c>
+    </row>
+    <row r="497" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A497" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="B497" s="5">
-        <v>100.208</v>
+        <v>100.2411</v>
       </c>
       <c r="C497" s="5">
-        <v>100.208</v>
-      </c>
-    </row>
-    <row r="498" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A498" s="13" t="s">
-        <v>28</v>
+        <v>100.4089</v>
+      </c>
+    </row>
+    <row r="498" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A498" t="s">
+        <v>7</v>
       </c>
       <c r="B498" s="5">
-        <v>100.2081</v>
+        <v>100.40900000000001</v>
       </c>
       <c r="C498" s="5">
-        <v>100.2409</v>
-      </c>
-    </row>
-    <row r="499" spans="1:3" s="13" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A499" s="13" t="s">
-        <v>27</v>
+        <v>100.43989999999999</v>
+      </c>
+    </row>
+    <row r="499" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A499" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="B499" s="5">
-        <v>100.241</v>
+        <v>100.44</v>
       </c>
       <c r="C499" s="5">
-        <v>100.241</v>
-      </c>
-    </row>
-    <row r="500" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A500" s="7" t="s">
+        <v>100.56989999999999</v>
+      </c>
+    </row>
+    <row r="500" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A500" t="s">
+        <v>7</v>
+      </c>
+      <c r="B500" s="5">
+        <v>100.57</v>
+      </c>
+      <c r="C500" s="5">
+        <v>100.74289999999999</v>
+      </c>
+    </row>
+    <row r="501" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A501" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B500" s="5">
-        <v>100.2411</v>
-      </c>
-      <c r="C500" s="5">
-        <v>100.4089</v>
-      </c>
-    </row>
-    <row r="501" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A501" t="s">
+      <c r="B501" s="5">
+        <v>100.74299999999999</v>
+      </c>
+      <c r="C501" s="5">
+        <v>100.94189999999999</v>
+      </c>
+    </row>
+    <row r="502" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A502" t="s">
         <v>7</v>
       </c>
-      <c r="B501" s="5">
-        <v>100.40900000000001</v>
-      </c>
-      <c r="C501" s="5">
-        <v>100.43989999999999</v>
-      </c>
-    </row>
-    <row r="502" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A502" s="7" t="s">
+      <c r="B502" s="5">
+        <v>100.94199999999999</v>
+      </c>
+      <c r="C502" s="5">
+        <v>100.99289999999999</v>
+      </c>
+    </row>
+    <row r="503" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A503" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B502" s="5">
-        <v>100.44</v>
-      </c>
-      <c r="C502" s="5">
-        <v>100.56989999999999</v>
-      </c>
-    </row>
-    <row r="503" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A503" t="s">
+      <c r="B503" s="5">
+        <v>100.99299999999999</v>
+      </c>
+      <c r="C503" s="5">
+        <v>101.19789999999999</v>
+      </c>
+    </row>
+    <row r="504" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A504" t="s">
         <v>7</v>
       </c>
-      <c r="B503" s="5">
-        <v>100.57</v>
-      </c>
-      <c r="C503" s="5">
-        <v>100.74289999999999</v>
-      </c>
-    </row>
-    <row r="504" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A504" s="7" t="s">
+      <c r="B504" s="5">
+        <v>101.19799999999999</v>
+      </c>
+      <c r="C504" s="5">
+        <v>101.51689999999999</v>
+      </c>
+    </row>
+    <row r="505" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A505" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B504" s="5">
-        <v>100.74299999999999</v>
-      </c>
-      <c r="C504" s="5">
-        <v>100.94189999999999</v>
-      </c>
-    </row>
-    <row r="505" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A505" t="s">
+      <c r="B505" s="5">
+        <v>101.517</v>
+      </c>
+      <c r="C505" s="5">
+        <v>101.8099</v>
+      </c>
+    </row>
+    <row r="506" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A506" t="s">
         <v>7</v>
       </c>
-      <c r="B505" s="5">
-        <v>100.94199999999999</v>
-      </c>
-      <c r="C505" s="5">
-        <v>100.99289999999999</v>
-      </c>
-    </row>
-    <row r="506" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A506" s="7" t="s">
+      <c r="B506" s="5">
+        <v>101.81</v>
+      </c>
+      <c r="C506" s="5">
+        <v>101.84389999999999</v>
+      </c>
+    </row>
+    <row r="507" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A507" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B506" s="5">
-        <v>100.99299999999999</v>
-      </c>
-      <c r="C506" s="5">
-        <v>101.19789999999999</v>
-      </c>
-    </row>
-    <row r="507" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A507" t="s">
+      <c r="B507" s="5">
+        <v>101.84399999999999</v>
+      </c>
+      <c r="C507" s="5">
+        <v>101.90089999999999</v>
+      </c>
+    </row>
+    <row r="508" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A508" t="s">
         <v>7</v>
       </c>
-      <c r="B507" s="5">
-        <v>101.19799999999999</v>
-      </c>
-      <c r="C507" s="5">
-        <v>101.51689999999999</v>
-      </c>
-    </row>
-    <row r="508" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A508" s="7" t="s">
+      <c r="B508" s="5">
+        <v>101.901</v>
+      </c>
+      <c r="C508" s="5">
+        <v>102.06189999999999</v>
+      </c>
+    </row>
+    <row r="509" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A509" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B508" s="5">
-        <v>101.517</v>
-      </c>
-      <c r="C508" s="5">
-        <v>101.8099</v>
-      </c>
-    </row>
-    <row r="509" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A509" t="s">
+      <c r="B509" s="5">
+        <v>102.062</v>
+      </c>
+      <c r="C509" s="5">
+        <v>102.14789999999999</v>
+      </c>
+    </row>
+    <row r="510" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A510" t="s">
         <v>7</v>
       </c>
-      <c r="B509" s="5">
-        <v>101.81</v>
-      </c>
-      <c r="C509" s="5">
-        <v>101.84389999999999</v>
-      </c>
-    </row>
-    <row r="510" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A510" s="7" t="s">
+      <c r="B510" s="5">
+        <v>102.148</v>
+      </c>
+      <c r="C510" s="5">
+        <v>102.18889999999999</v>
+      </c>
+    </row>
+    <row r="511" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A511" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B510" s="5">
-        <v>101.84399999999999</v>
-      </c>
-      <c r="C510" s="5">
-        <v>101.90089999999999</v>
-      </c>
-    </row>
-    <row r="511" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A511" t="s">
+      <c r="B511" s="5">
+        <v>102.18899999999999</v>
+      </c>
+      <c r="C511" s="5">
+        <v>102.3109</v>
+      </c>
+    </row>
+    <row r="512" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A512" t="s">
         <v>7</v>
       </c>
-      <c r="B511" s="5">
-        <v>101.901</v>
-      </c>
-      <c r="C511" s="5">
-        <v>102.06189999999999</v>
-      </c>
-    </row>
-    <row r="512" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A512" s="7" t="s">
+      <c r="B512" s="5">
+        <v>102.31100000000001</v>
+      </c>
+      <c r="C512" s="5">
+        <v>102.3609</v>
+      </c>
+    </row>
+    <row r="513" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A513" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B512" s="5">
-        <v>102.062</v>
-      </c>
-      <c r="C512" s="5">
-        <v>102.14789999999999</v>
-      </c>
-    </row>
-    <row r="513" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A513" t="s">
+      <c r="B513" s="5">
+        <v>102.361</v>
+      </c>
+      <c r="C513" s="5">
+        <v>102.79089999999999</v>
+      </c>
+    </row>
+    <row r="514" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A514" t="s">
         <v>7</v>
       </c>
-      <c r="B513" s="5">
-        <v>102.148</v>
-      </c>
-      <c r="C513" s="5">
-        <v>102.18889999999999</v>
-      </c>
-    </row>
-    <row r="514" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A514" s="7" t="s">
+      <c r="B514" s="5">
+        <v>102.791</v>
+      </c>
+      <c r="C514" s="5">
+        <v>102.9909</v>
+      </c>
+    </row>
+    <row r="515" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A515" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B514" s="5">
-        <v>102.18899999999999</v>
-      </c>
-      <c r="C514" s="5">
-        <v>102.3109</v>
-      </c>
-    </row>
-    <row r="515" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A515" t="s">
+      <c r="B515" s="5">
+        <v>102.991</v>
+      </c>
+      <c r="C515" s="5">
+        <v>103.22789999999999</v>
+      </c>
+    </row>
+    <row r="516" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A516" t="s">
         <v>7</v>
       </c>
-      <c r="B515" s="5">
-        <v>102.31100000000001</v>
-      </c>
-      <c r="C515" s="5">
-        <v>102.3609</v>
-      </c>
-    </row>
-    <row r="516" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A516" s="7" t="s">
+      <c r="B516" s="5">
+        <v>103.22799999999999</v>
+      </c>
+      <c r="C516" s="5">
+        <v>103.52889999999999</v>
+      </c>
+    </row>
+    <row r="517" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A517" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B516" s="5">
-        <v>102.361</v>
-      </c>
-      <c r="C516" s="5">
-        <v>102.79089999999999</v>
-      </c>
-    </row>
-    <row r="517" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A517" t="s">
+      <c r="B517" s="5">
+        <v>103.529</v>
+      </c>
+      <c r="C517" s="5">
+        <v>103.6859</v>
+      </c>
+    </row>
+    <row r="518" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A518" t="s">
         <v>7</v>
       </c>
-      <c r="B517" s="5">
-        <v>102.791</v>
-      </c>
-      <c r="C517" s="5">
-        <v>102.9909</v>
-      </c>
-    </row>
-    <row r="518" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A518" s="7" t="s">
+      <c r="B518" s="5">
+        <v>103.68600000000001</v>
+      </c>
+      <c r="C518" s="5">
+        <v>103.88289999999999</v>
+      </c>
+    </row>
+    <row r="519" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A519" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B518" s="5">
-        <v>102.991</v>
-      </c>
-      <c r="C518" s="5">
-        <v>103.22789999999999</v>
-      </c>
-    </row>
-    <row r="519" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A519" t="s">
+      <c r="B519" s="5">
+        <v>103.883</v>
+      </c>
+      <c r="C519" s="5">
+        <v>104.05289999999999</v>
+      </c>
+    </row>
+    <row r="520" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A520" t="s">
         <v>7</v>
       </c>
-      <c r="B519" s="5">
-        <v>103.22799999999999</v>
-      </c>
-      <c r="C519" s="5">
-        <v>103.52889999999999</v>
-      </c>
-    </row>
-    <row r="520" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A520" s="7" t="s">
+      <c r="B520" s="5">
+        <v>104.053</v>
+      </c>
+      <c r="C520" s="5">
+        <v>104.1439</v>
+      </c>
+    </row>
+    <row r="521" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A521" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B520" s="5">
-        <v>103.529</v>
-      </c>
-      <c r="C520" s="5">
-        <v>103.6859</v>
-      </c>
-    </row>
-    <row r="521" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A521" t="s">
+      <c r="B521" s="5">
+        <v>104.14400000000001</v>
+      </c>
+      <c r="C521" s="5">
+        <v>106.0219</v>
+      </c>
+    </row>
+    <row r="522" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A522" t="s">
         <v>7</v>
       </c>
-      <c r="B521" s="5">
-        <v>103.68600000000001</v>
-      </c>
-      <c r="C521" s="5">
-        <v>103.88289999999999</v>
-      </c>
-    </row>
-    <row r="522" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A522" s="7" t="s">
+      <c r="B522" s="5">
+        <v>106.02200000000001</v>
+      </c>
+      <c r="C522" s="5">
+        <v>106.0779</v>
+      </c>
+    </row>
+    <row r="523" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A523" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B522" s="5">
-        <v>103.883</v>
-      </c>
-      <c r="C522" s="5">
-        <v>104.05289999999999</v>
-      </c>
-    </row>
-    <row r="523" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A523" t="s">
+      <c r="B523" s="5">
+        <v>106.078</v>
+      </c>
+      <c r="C523" s="5">
+        <v>106.4079</v>
+      </c>
+    </row>
+    <row r="524" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A524" t="s">
         <v>7</v>
       </c>
-      <c r="B523" s="5">
-        <v>104.053</v>
-      </c>
-      <c r="C523" s="5">
-        <v>104.1439</v>
-      </c>
-    </row>
-    <row r="524" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A524" s="7" t="s">
+      <c r="B524" s="5">
+        <v>106.408</v>
+      </c>
+      <c r="C524" s="5">
+        <v>106.85589999999999</v>
+      </c>
+    </row>
+    <row r="525" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A525" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B524" s="5">
-        <v>104.14400000000001</v>
-      </c>
-      <c r="C524" s="5">
-        <v>106.0219</v>
-      </c>
-    </row>
-    <row r="525" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A525" t="s">
+      <c r="B525" s="5">
+        <v>106.85599999999999</v>
+      </c>
+      <c r="C525" s="5">
+        <v>107.0749</v>
+      </c>
+    </row>
+    <row r="526" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A526" t="s">
         <v>7</v>
       </c>
-      <c r="B525" s="5">
-        <v>106.02200000000001</v>
-      </c>
-      <c r="C525" s="5">
-        <v>106.0779</v>
-      </c>
-    </row>
-    <row r="526" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A526" s="7" t="s">
+      <c r="B526" s="5">
+        <v>107.075</v>
+      </c>
+      <c r="C526" s="5">
+        <v>107.1249</v>
+      </c>
+    </row>
+    <row r="527" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A527" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B526" s="5">
-        <v>106.078</v>
-      </c>
-      <c r="C526" s="5">
-        <v>106.4079</v>
-      </c>
-    </row>
-    <row r="527" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A527" t="s">
+      <c r="B527" s="5">
+        <v>107.125</v>
+      </c>
+      <c r="C527" s="5">
+        <v>107.1939</v>
+      </c>
+    </row>
+    <row r="528" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A528" t="s">
         <v>7</v>
       </c>
-      <c r="B527" s="5">
-        <v>106.408</v>
-      </c>
-      <c r="C527" s="5">
-        <v>106.85589999999999</v>
-      </c>
-    </row>
-    <row r="528" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A528" s="7" t="s">
+      <c r="B528" s="5">
+        <v>107.194</v>
+      </c>
+      <c r="C528" s="5">
+        <v>107.2409</v>
+      </c>
+    </row>
+    <row r="529" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A529" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B528" s="5">
-        <v>106.85599999999999</v>
-      </c>
-      <c r="C528" s="5">
-        <v>107.0749</v>
-      </c>
-    </row>
-    <row r="529" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A529" t="s">
+      <c r="B529" s="5">
+        <v>107.241</v>
+      </c>
+      <c r="C529" s="5">
+        <v>107.6039</v>
+      </c>
+    </row>
+    <row r="530" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A530" t="s">
         <v>7</v>
       </c>
-      <c r="B529" s="5">
-        <v>107.075</v>
-      </c>
-      <c r="C529" s="5">
-        <v>107.1249</v>
-      </c>
-    </row>
-    <row r="530" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A530" s="7" t="s">
+      <c r="B530" s="5">
+        <v>107.604</v>
+      </c>
+      <c r="C530" s="5">
+        <v>107.8049</v>
+      </c>
+    </row>
+    <row r="531" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A531" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B530" s="5">
-        <v>107.125</v>
-      </c>
-      <c r="C530" s="5">
-        <v>107.1939</v>
-      </c>
-    </row>
-    <row r="531" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A531" t="s">
+      <c r="B531" s="5">
+        <v>107.80500000000001</v>
+      </c>
+      <c r="C531" s="5">
+        <v>107.8969</v>
+      </c>
+    </row>
+    <row r="532" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A532" t="s">
         <v>7</v>
       </c>
-      <c r="B531" s="5">
-        <v>107.194</v>
-      </c>
-      <c r="C531" s="5">
-        <v>107.2409</v>
-      </c>
-    </row>
-    <row r="532" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A532" s="7" t="s">
+      <c r="B532" s="5">
+        <v>107.89700000000001</v>
+      </c>
+      <c r="C532" s="5">
+        <v>108.0369</v>
+      </c>
+    </row>
+    <row r="533" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A533" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B532" s="5">
-        <v>107.241</v>
-      </c>
-      <c r="C532" s="5">
-        <v>107.6039</v>
-      </c>
-    </row>
-    <row r="533" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A533" t="s">
+      <c r="B533" s="5">
+        <v>108.03700000000001</v>
+      </c>
+      <c r="C533" s="5">
+        <v>108.4229</v>
+      </c>
+    </row>
+    <row r="534" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A534" t="s">
         <v>7</v>
       </c>
-      <c r="B533" s="5">
-        <v>107.604</v>
-      </c>
-      <c r="C533" s="5">
-        <v>107.8049</v>
-      </c>
-    </row>
-    <row r="534" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A534" s="7" t="s">
+      <c r="B534" s="5">
+        <v>108.423</v>
+      </c>
+      <c r="C534" s="5">
+        <v>108.88589999999999</v>
+      </c>
+    </row>
+    <row r="535" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A535" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B534" s="5">
-        <v>107.80500000000001</v>
-      </c>
-      <c r="C534" s="5">
-        <v>107.8969</v>
-      </c>
-    </row>
-    <row r="535" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A535" t="s">
+      <c r="B535" s="5">
+        <v>108.886</v>
+      </c>
+      <c r="C535" s="5">
+        <v>109.2439</v>
+      </c>
+    </row>
+    <row r="536" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A536" t="s">
         <v>7</v>
       </c>
-      <c r="B535" s="5">
-        <v>107.89700000000001</v>
-      </c>
-      <c r="C535" s="5">
-        <v>108.0369</v>
-      </c>
-    </row>
-    <row r="536" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A536" s="7" t="s">
+      <c r="B536" s="5">
+        <v>109.244</v>
+      </c>
+      <c r="C536" s="5">
+        <v>109.36789999999999</v>
+      </c>
+    </row>
+    <row r="537" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A537" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B536" s="5">
-        <v>108.03700000000001</v>
-      </c>
-      <c r="C536" s="5">
-        <v>108.4229</v>
-      </c>
-    </row>
-    <row r="537" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A537" t="s">
+      <c r="B537" s="5">
+        <v>109.36799999999999</v>
+      </c>
+      <c r="C537" s="5">
+        <v>110.3569</v>
+      </c>
+    </row>
+    <row r="538" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A538" t="s">
         <v>7</v>
       </c>
-      <c r="B537" s="5">
-        <v>108.423</v>
-      </c>
-      <c r="C537" s="5">
-        <v>108.88589999999999</v>
-      </c>
-    </row>
-    <row r="538" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A538" s="7" t="s">
+      <c r="B538" s="5">
+        <v>110.357</v>
+      </c>
+      <c r="C538" s="5">
+        <v>110.3819</v>
+      </c>
+    </row>
+    <row r="539" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A539" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B538" s="5">
-        <v>108.886</v>
-      </c>
-      <c r="C538" s="5">
-        <v>109.2439</v>
-      </c>
-    </row>
-    <row r="539" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A539" t="s">
+      <c r="B539" s="5">
+        <v>110.38200000000001</v>
+      </c>
+      <c r="C539" s="5">
+        <v>110.56189999999999</v>
+      </c>
+    </row>
+    <row r="540" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A540" t="s">
         <v>7</v>
       </c>
-      <c r="B539" s="5">
-        <v>109.244</v>
-      </c>
-      <c r="C539" s="5">
-        <v>109.36789999999999</v>
-      </c>
-    </row>
-    <row r="540" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A540" s="7" t="s">
+      <c r="B540" s="5">
+        <v>110.562</v>
+      </c>
+      <c r="C540" s="5">
+        <v>110.7469</v>
+      </c>
+    </row>
+    <row r="541" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A541" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B540" s="5">
-        <v>109.36799999999999</v>
-      </c>
-      <c r="C540" s="5">
-        <v>110.3569</v>
-      </c>
-    </row>
-    <row r="541" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A541" t="s">
+      <c r="B541" s="5">
+        <v>110.747</v>
+      </c>
+      <c r="C541" s="5">
+        <v>111.27289999999999</v>
+      </c>
+    </row>
+    <row r="542" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A542" t="s">
         <v>7</v>
       </c>
-      <c r="B541" s="5">
-        <v>110.357</v>
-      </c>
-      <c r="C541" s="5">
-        <v>110.3819</v>
-      </c>
-    </row>
-    <row r="542" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A542" s="7" t="s">
+      <c r="B542" s="5">
+        <v>111.273</v>
+      </c>
+      <c r="C542" s="5">
+        <v>111.5869</v>
+      </c>
+    </row>
+    <row r="543" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A543" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B542" s="5">
-        <v>110.38200000000001</v>
-      </c>
-      <c r="C542" s="5">
-        <v>110.56189999999999</v>
-      </c>
-    </row>
-    <row r="543" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A543" t="s">
+      <c r="B543" s="5">
+        <v>111.587</v>
+      </c>
+      <c r="C543" s="5">
+        <v>112.0919</v>
+      </c>
+    </row>
+    <row r="544" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A544" t="s">
         <v>7</v>
       </c>
-      <c r="B543" s="5">
-        <v>110.562</v>
-      </c>
-      <c r="C543" s="5">
-        <v>110.7469</v>
-      </c>
-    </row>
-    <row r="544" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A544" s="7" t="s">
-        <v>13</v>
-      </c>
       <c r="B544" s="5">
-        <v>110.747</v>
-      </c>
-      <c r="C544" s="5">
-        <v>111.27289999999999</v>
-      </c>
-    </row>
-    <row r="545" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A545" t="s">
-        <v>7</v>
-      </c>
-      <c r="B545" s="5">
-        <v>111.273</v>
-      </c>
-      <c r="C545" s="5">
-        <v>111.5869</v>
-      </c>
-    </row>
-    <row r="546" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A546" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B546" s="5">
-        <v>111.587</v>
-      </c>
-      <c r="C546" s="5">
-        <v>112.0919</v>
-      </c>
-    </row>
-    <row r="547" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A547" t="s">
-        <v>7</v>
-      </c>
-      <c r="B547" s="5">
         <v>112.092</v>
       </c>
-      <c r="C547" s="8">
+      <c r="C544" s="8">
         <v>113.5</v>
       </c>
     </row>
@@ -16123,15 +16086,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
   <Receiver>
@@ -16181,7 +16135,7 @@
 </spe:Receivers>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <Descriptive_x0020_Name xmlns="c32bb4e5-d30f-47c7-b40d-8e40c9a47274" xsi:nil="true"/>
@@ -16203,7 +16157,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003400CA90578C4C4DACE963633D340941" ma:contentTypeVersion="124" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d6014bca55b54fb6e72613884150ba92">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c32bb4e5-d30f-47c7-b40d-8e40c9a47274" xmlns:ns3="f57c62ac-5b60-40b7-9460-0473ac1a050a" xmlns:ns4="a4282dde-c91e-40c5-9bfe-d2af68f8b118" xmlns:ns5="http://schemas.microsoft.com/sharepoint/v4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9291523fd70371bbc058d49edbaeafd7" ns2:_="" ns3:_="" ns4:_="" ns5:_="">
     <xsd:import namespace="c32bb4e5-d30f-47c7-b40d-8e40c9a47274"/>
@@ -16428,19 +16382,24 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{357E1FF0-4A64-4798-9334-EA214FC91C3F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{366A783D-DD4A-4A1A-95A1-DD398838B18A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{366A783D-DD4A-4A1A-95A1-DD398838B18A}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B0B93CE-FB0F-49C2-997B-02D54C292B78}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -16448,10 +16407,37 @@
     <ds:schemaRef ds:uri="c32bb4e5-d30f-47c7-b40d-8e40c9a47274"/>
     <ds:schemaRef ds:uri="9ecf1a6e-3aad-4311-93bc-48574f90e2b0"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v4"/>
+    <ds:schemaRef ds:uri="a4282dde-c91e-40c5-9bfe-d2af68f8b118"/>
+    <ds:schemaRef ds:uri="f57c62ac-5b60-40b7-9460-0473ac1a050a"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3052DB8-E931-4143-8D13-5AD49243405F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="c32bb4e5-d30f-47c7-b40d-8e40c9a47274"/>
+    <ds:schemaRef ds:uri="f57c62ac-5b60-40b7-9460-0473ac1a050a"/>
+    <ds:schemaRef ds:uri="a4282dde-c91e-40c5-9bfe-d2af68f8b118"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v4"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3052DB8-E931-4143-8D13-5AD49243405F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{357E1FF0-4A64-4798-9334-EA214FC91C3F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>